--- a/file3.xlsx
+++ b/file3.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27221"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="1200" documentId="13_ncr:1_{0F4043DC-AE40-40C5-B5E1-94FF7E927464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18DE2B92-0F0D-40FF-A64C-564617E91403}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B17E8B-81AC-4B95-8921-3C85D95B1788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11895" yWindow="-21720" windowWidth="51840" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-9740" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lista Apparati AnnexA" sheetId="4" r:id="rId1"/>
@@ -1444,7 +1444,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1962,12 +1962,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2008,877 +2002,17 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="62">
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2948,6 +2082,872 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3059,130 +3059,130 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{31E540E7-E1A9-4012-B9C5-24BE6846CE10}" name="Tabella3" displayName="Tabella3" ref="F1:F4" totalsRowShown="0" headerRowDxfId="54" headerRowBorderDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{31E540E7-E1A9-4012-B9C5-24BE6846CE10}" name="Tabella3" displayName="Tabella3" ref="F1:F4" totalsRowShown="0" headerRowDxfId="61" headerRowBorderDxfId="60">
   <autoFilter ref="F1:F4" xr:uid="{31E540E7-E1A9-4012-B9C5-24BE6846CE10}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{3F719A62-88CF-458F-BA64-DD2482E1263B}" name="SNMP" dataDxfId="52"/>
+    <tableColumn id="1" xr3:uid="{3F719A62-88CF-458F-BA64-DD2482E1263B}" name="SNMP" dataDxfId="59"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{A666E552-923F-4196-9739-6A2B2A0B9632}" name="Tabella11" displayName="Tabella11" ref="V1:V5" totalsRowShown="0" headerRowDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{A666E552-923F-4196-9739-6A2B2A0B9632}" name="Tabella11" displayName="Tabella11" ref="V1:V5" totalsRowShown="0" headerRowDxfId="20">
   <autoFilter ref="V1:V5" xr:uid="{A666E552-923F-4196-9739-6A2B2A0B9632}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{556B8EF8-CA65-4015-B664-50434A25316A}" name="Severity" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{556B8EF8-CA65-4015-B664-50434A25316A}" name="Severity" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{CE23E324-F8DB-45B7-AD44-18EA595BF033}" name="Tabella12" displayName="Tabella12" ref="X1:X6" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{CE23E324-F8DB-45B7-AD44-18EA595BF033}" name="Tabella12" displayName="Tabella12" ref="X1:X6" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <autoFilter ref="X1:X6" xr:uid="{CE23E324-F8DB-45B7-AD44-18EA595BF033}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{059DBE1F-FC22-44F7-9528-A081223FA567}" name="SLA" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{059DBE1F-FC22-44F7-9528-A081223FA567}" name="SLA" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{4E1E3E1B-9372-46D9-8074-E24874C079C3}" name="Tabella1114" displayName="Tabella1114" ref="Z1:Z4" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{4E1E3E1B-9372-46D9-8074-E24874C079C3}" name="Tabella1114" displayName="Tabella1114" ref="Z1:Z4" totalsRowShown="0" headerRowDxfId="15" headerRowBorderDxfId="14" tableBorderDxfId="13" totalsRowBorderDxfId="12">
   <autoFilter ref="Z1:Z4" xr:uid="{4E1E3E1B-9372-46D9-8074-E24874C079C3}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{1466B9FE-12B7-418D-9FAA-FC6A6BF311B6}" name="Monitoraggio" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{1466B9FE-12B7-418D-9FAA-FC6A6BF311B6}" name="Monitoraggio" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{748D7A7B-6935-464F-B806-AF21508A38BF}" name="Tabella215" displayName="Tabella215" ref="B1:B10" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="1" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{748D7A7B-6935-464F-B806-AF21508A38BF}" name="Tabella215" displayName="Tabella215" ref="B1:B10" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8">
   <autoFilter ref="B1:B10" xr:uid="{748D7A7B-6935-464F-B806-AF21508A38BF}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{9BA91E74-1457-438B-9DA7-0045ED972429}" name="Device Role" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{9BA91E74-1457-438B-9DA7-0045ED972429}" name="Device Role" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{92C502AF-0B8F-465F-848B-1DB7DFA66908}" name="Tabella4" displayName="Tabella4" ref="H1:H13" totalsRowShown="0" headerRowDxfId="51" headerRowBorderDxfId="49" tableBorderDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{92C502AF-0B8F-465F-848B-1DB7DFA66908}" name="Tabella4" displayName="Tabella4" ref="H1:H13" totalsRowShown="0" headerRowDxfId="58" headerRowBorderDxfId="57" tableBorderDxfId="56">
   <autoFilter ref="H1:H13" xr:uid="{92C502AF-0B8F-465F-848B-1DB7DFA66908}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{14462602-F05C-418B-AB80-4F8EF74C66A6}" name="Platform" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{14462602-F05C-418B-AB80-4F8EF74C66A6}" name="Platform" dataDxfId="55"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{499F8EA1-0CE0-412B-BC25-882F57A1A1EC}" name="Tabella5" displayName="Tabella5" ref="L1:L11" totalsRowShown="0" headerRowDxfId="47" headerRowBorderDxfId="45" tableBorderDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{499F8EA1-0CE0-412B-BC25-882F57A1A1EC}" name="Tabella5" displayName="Tabella5" ref="L1:L11" totalsRowShown="0" headerRowDxfId="54" headerRowBorderDxfId="53" tableBorderDxfId="52">
   <autoFilter ref="L1:L11" xr:uid="{499F8EA1-0CE0-412B-BC25-882F57A1A1EC}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{72F9D126-94C2-4CF5-BF7E-FFEB68588C4B}" name="Manufacturers" dataDxfId="44"/>
+    <tableColumn id="1" xr3:uid="{72F9D126-94C2-4CF5-BF7E-FFEB68588C4B}" name="Manufacturers" dataDxfId="51"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{364F1AA0-0572-4F07-8AC7-CF8DED01B8F4}" name="Tabella6" displayName="Tabella6" ref="D1:D8" totalsRowShown="0" headerRowDxfId="43" headerRowBorderDxfId="41" tableBorderDxfId="42" totalsRowBorderDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{364F1AA0-0572-4F07-8AC7-CF8DED01B8F4}" name="Tabella6" displayName="Tabella6" ref="D1:D8" totalsRowShown="0" headerRowDxfId="50" headerRowBorderDxfId="49" tableBorderDxfId="48" totalsRowBorderDxfId="47">
   <autoFilter ref="D1:D8" xr:uid="{364F1AA0-0572-4F07-8AC7-CF8DED01B8F4}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{FB0C75CE-DA45-4868-BF66-CB2A1013782D}" name="Status" dataDxfId="39"/>
+    <tableColumn id="1" xr3:uid="{FB0C75CE-DA45-4868-BF66-CB2A1013782D}" name="Status" dataDxfId="46"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{5E8FEB17-D02F-406D-89A9-A5900D0D20FA}" name="Tabella7" displayName="Tabella7" ref="J1:J7" totalsRowShown="0" headerRowDxfId="38" headerRowBorderDxfId="36" tableBorderDxfId="37" totalsRowBorderDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{5E8FEB17-D02F-406D-89A9-A5900D0D20FA}" name="Tabella7" displayName="Tabella7" ref="J1:J7" totalsRowShown="0" headerRowDxfId="45" headerRowBorderDxfId="44" tableBorderDxfId="43" totalsRowBorderDxfId="42">
   <autoFilter ref="J1:J7" xr:uid="{5E8FEB17-D02F-406D-89A9-A5900D0D20FA}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{85763B72-65A7-42D8-9A13-5A5313E71A3F}" name="Connection Type" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{85763B72-65A7-42D8-9A13-5A5313E71A3F}" name="Connection Type" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{170B9570-185E-4946-B59D-05C130944C17}" name="Tabella8" displayName="Tabella8" ref="N1:N6" totalsRowShown="0" headerRowDxfId="33" headerRowBorderDxfId="31" tableBorderDxfId="32" totalsRowBorderDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{170B9570-185E-4946-B59D-05C130944C17}" name="Tabella8" displayName="Tabella8" ref="N1:N6" totalsRowShown="0" headerRowDxfId="40" headerRowBorderDxfId="39" tableBorderDxfId="38" totalsRowBorderDxfId="37">
   <autoFilter ref="N1:N6" xr:uid="{170B9570-185E-4946-B59D-05C130944C17}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{4BAD1F16-CDD6-41E5-AA6F-A54BEF3A5C09}" name="Network Layer" dataDxfId="29"/>
+    <tableColumn id="1" xr3:uid="{4BAD1F16-CDD6-41E5-AA6F-A54BEF3A5C09}" name="Network Layer" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{07363CAA-9A0F-44AB-8658-DBCF0FF48F41}" name="Tabella9" displayName="Tabella9" ref="P1:P6" totalsRowShown="0" headerRowDxfId="28" headerRowBorderDxfId="26" tableBorderDxfId="27" totalsRowBorderDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{07363CAA-9A0F-44AB-8658-DBCF0FF48F41}" name="Tabella9" displayName="Tabella9" ref="P1:P6" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
   <autoFilter ref="P1:P6" xr:uid="{07363CAA-9A0F-44AB-8658-DBCF0FF48F41}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{7885F357-6C90-4843-ABE8-5FDBBC2D691F}" name="On site" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{7885F357-6C90-4843-ABE8-5FDBBC2D691F}" name="On site" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{70181979-135C-44D3-A63C-79BEDF93C8C5}" name="Tabella10" displayName="Tabella10" ref="R1:R6" totalsRowShown="0" headerRowDxfId="23" headerRowBorderDxfId="21" tableBorderDxfId="22" totalsRowBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{70181979-135C-44D3-A63C-79BEDF93C8C5}" name="Tabella10" displayName="Tabella10" ref="R1:R6" totalsRowShown="0" headerRowDxfId="30" headerRowBorderDxfId="29" tableBorderDxfId="28" totalsRowBorderDxfId="27">
   <autoFilter ref="R1:R6" xr:uid="{70181979-135C-44D3-A63C-79BEDF93C8C5}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{6B907CA0-6606-4963-9133-D43CC34E47E6}" name="Maintenance" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{6B907CA0-6606-4963-9133-D43CC34E47E6}" name="Maintenance" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2F328F9D-EC69-4ED4-B6FE-75ED0F2A1DE8}" name="Tabella1" displayName="Tabella1" ref="T1:T243" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="16" tableBorderDxfId="17" totalsRowBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2F328F9D-EC69-4ED4-B6FE-75ED0F2A1DE8}" name="Tabella1" displayName="Tabella1" ref="T1:T243" totalsRowShown="0" headerRowDxfId="25" headerRowBorderDxfId="24" tableBorderDxfId="23" totalsRowBorderDxfId="22">
   <autoFilter ref="T1:T243" xr:uid="{2F328F9D-EC69-4ED4-B6FE-75ED0F2A1DE8}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{82A1CA76-1045-4C56-84AB-C137BD923ED0}" name="Location" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{82A1CA76-1045-4C56-84AB-C137BD923ED0}" name="Location" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3511,37 +3511,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0B4B0D9-5502-4206-8124-058726D7F555}">
   <dimension ref="A1:AA46"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.42578125" style="39" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.44140625" style="39" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="16" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -3624,35 +3624,35 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
-      <c r="A2" s="56" t="s">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A2" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="D2" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="57">
+      <c r="E2" s="55">
         <v>5229821415</v>
       </c>
-      <c r="F2" s="56" t="s">
+      <c r="F2" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="58" t="s">
+      <c r="G2" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="56" t="s">
+      <c r="H2" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="56" t="s">
+      <c r="I2" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="56" t="s">
+      <c r="J2" s="54" t="s">
         <v>35</v>
       </c>
       <c r="K2" s="44">
@@ -3665,68 +3665,68 @@
         <v>37</v>
       </c>
       <c r="N2" s="41"/>
-      <c r="O2" s="56" t="s">
+      <c r="O2" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P2" s="56" t="s">
+      <c r="P2" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q2" s="59"/>
+      <c r="Q2" s="57"/>
       <c r="R2" s="45">
         <v>44926</v>
       </c>
-      <c r="S2" s="60">
+      <c r="S2" s="58">
         <v>45291</v>
       </c>
-      <c r="T2" s="57" t="s">
+      <c r="T2" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="U2" s="61" t="s">
+      <c r="U2" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V2" s="62" t="s">
+      <c r="V2" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="W2" s="56"/>
-      <c r="X2" s="56" t="s">
+      <c r="W2" s="54"/>
+      <c r="X2" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="Y2" s="56" t="s">
+      <c r="Y2" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z2" s="56" t="s">
+      <c r="Z2" s="54" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:27">
-      <c r="A3" s="56" t="s">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A3" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="57" t="s">
+      <c r="C3" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="57" t="s">
+      <c r="D3" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="57">
+      <c r="E3" s="55">
         <v>214948846</v>
       </c>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="58" t="s">
+      <c r="G3" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="56" t="s">
+      <c r="H3" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="56" t="s">
+      <c r="I3" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="56" t="s">
+      <c r="J3" s="54" t="s">
         <v>35</v>
       </c>
       <c r="K3" s="46" t="s">
@@ -3739,71 +3739,71 @@
         <v>37</v>
       </c>
       <c r="N3" s="42"/>
-      <c r="O3" s="56" t="s">
+      <c r="O3" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P3" s="56" t="s">
+      <c r="P3" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q3" s="59"/>
+      <c r="Q3" s="57"/>
       <c r="R3" s="45">
         <v>44926</v>
       </c>
-      <c r="S3" s="60">
+      <c r="S3" s="58">
         <v>45291</v>
       </c>
-      <c r="T3" s="57" t="s">
+      <c r="T3" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U3" s="61" t="s">
+      <c r="U3" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V3" s="62" t="s">
+      <c r="V3" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="56"/>
-      <c r="X3" s="56" t="s">
+      <c r="W3" s="54"/>
+      <c r="X3" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y3" s="56" t="s">
+      <c r="Y3" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z3" s="56" t="s">
+      <c r="Z3" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:27">
-      <c r="A4" s="56" t="s">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A4" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="57" t="s">
+      <c r="D4" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="57">
+      <c r="E4" s="55">
         <v>214948414</v>
       </c>
-      <c r="F4" s="56" t="s">
+      <c r="F4" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="58" t="s">
+      <c r="G4" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="56" t="s">
+      <c r="H4" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="56" t="s">
+      <c r="I4" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="56" t="s">
+      <c r="J4" s="54" t="s">
         <v>35</v>
       </c>
       <c r="K4" s="46" t="s">
@@ -3816,71 +3816,71 @@
         <v>37</v>
       </c>
       <c r="N4" s="42"/>
-      <c r="O4" s="56" t="s">
+      <c r="O4" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P4" s="56" t="s">
+      <c r="P4" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q4" s="59"/>
+      <c r="Q4" s="57"/>
       <c r="R4" s="45">
         <v>44926</v>
       </c>
-      <c r="S4" s="60">
+      <c r="S4" s="58">
         <v>45291</v>
       </c>
-      <c r="T4" s="57" t="s">
+      <c r="T4" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U4" s="61" t="s">
+      <c r="U4" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V4" s="62" t="s">
+      <c r="V4" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W4" s="56"/>
-      <c r="X4" s="56" t="s">
+      <c r="W4" s="54"/>
+      <c r="X4" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y4" s="56" t="s">
+      <c r="Y4" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z4" s="56" t="s">
+      <c r="Z4" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:27">
-      <c r="A5" s="61" t="s">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A5" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="57" t="s">
+      <c r="C5" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="57" t="s">
+      <c r="D5" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="57">
+      <c r="E5" s="55">
         <v>1500730058</v>
       </c>
-      <c r="F5" s="56" t="s">
+      <c r="F5" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="58" t="s">
+      <c r="G5" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="56" t="s">
+      <c r="H5" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="56" t="s">
+      <c r="I5" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="56" t="s">
+      <c r="J5" s="54" t="s">
         <v>35</v>
       </c>
       <c r="K5" s="46" t="s">
@@ -3893,69 +3893,69 @@
         <v>37</v>
       </c>
       <c r="N5" s="42"/>
-      <c r="O5" s="56" t="s">
+      <c r="O5" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P5" s="56" t="s">
+      <c r="P5" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q5" s="59"/>
+      <c r="Q5" s="57"/>
       <c r="R5" s="45">
         <v>44926</v>
       </c>
-      <c r="S5" s="60">
+      <c r="S5" s="58">
         <v>45291</v>
       </c>
-      <c r="T5" s="57" t="s">
+      <c r="T5" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U5" s="61" t="s">
+      <c r="U5" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V5" s="62" t="s">
+      <c r="V5" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="W5" s="56"/>
-      <c r="X5" s="56" t="s">
+      <c r="W5" s="54"/>
+      <c r="X5" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y5" s="56" t="s">
+      <c r="Y5" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z5" s="56" t="s">
+      <c r="Z5" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:27">
-      <c r="A6" s="61" t="s">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A6" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="57" t="s">
+      <c r="C6" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="57" t="s">
+      <c r="D6" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="63"/>
-      <c r="F6" s="56" t="s">
+      <c r="E6" s="61"/>
+      <c r="F6" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="58" t="s">
+      <c r="G6" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="56" t="s">
+      <c r="H6" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="56" t="s">
+      <c r="I6" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="56" t="s">
+      <c r="J6" s="54" t="s">
         <v>35</v>
       </c>
       <c r="K6" s="46" t="s">
@@ -3968,71 +3968,71 @@
         <v>37</v>
       </c>
       <c r="N6" s="42"/>
-      <c r="O6" s="56" t="s">
+      <c r="O6" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="56" t="s">
+      <c r="P6" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="59"/>
+      <c r="Q6" s="57"/>
       <c r="R6" s="45">
         <v>44926</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="58">
         <v>45291</v>
       </c>
-      <c r="T6" s="57" t="s">
+      <c r="T6" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U6" s="61" t="s">
+      <c r="U6" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V6" s="62" t="s">
+      <c r="V6" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="W6" s="56"/>
-      <c r="X6" s="56" t="s">
+      <c r="W6" s="54"/>
+      <c r="X6" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y6" s="56" t="s">
+      <c r="Y6" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z6" s="56" t="s">
+      <c r="Z6" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
-      <c r="A7" s="56" t="s">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A7" s="54" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="56" t="s">
+      <c r="B7" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="57" t="s">
+      <c r="C7" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="57" t="s">
+      <c r="D7" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="57">
+      <c r="E7" s="55">
         <v>209227339</v>
       </c>
-      <c r="F7" s="56" t="s">
+      <c r="F7" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="58" t="s">
+      <c r="G7" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="56" t="s">
+      <c r="H7" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="56" t="s">
+      <c r="I7" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="56" t="s">
+      <c r="J7" s="54" t="s">
         <v>35</v>
       </c>
       <c r="K7" s="46" t="s">
@@ -4045,71 +4045,71 @@
         <v>37</v>
       </c>
       <c r="N7" s="42"/>
-      <c r="O7" s="56" t="s">
+      <c r="O7" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P7" s="56" t="s">
+      <c r="P7" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q7" s="59"/>
+      <c r="Q7" s="57"/>
       <c r="R7" s="45">
         <v>44926</v>
       </c>
-      <c r="S7" s="60">
+      <c r="S7" s="58">
         <v>45291</v>
       </c>
-      <c r="T7" s="57" t="s">
+      <c r="T7" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U7" s="61" t="s">
+      <c r="U7" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V7" s="62" t="s">
+      <c r="V7" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W7" s="56"/>
-      <c r="X7" s="56" t="s">
+      <c r="W7" s="54"/>
+      <c r="X7" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y7" s="56" t="s">
+      <c r="Y7" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z7" s="56" t="s">
+      <c r="Z7" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:27">
-      <c r="A8" s="56" t="s">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A8" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="56" t="s">
+      <c r="B8" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="57" t="s">
+      <c r="C8" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="D8" s="57" t="s">
+      <c r="D8" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="57">
+      <c r="E8" s="55">
         <v>239867844</v>
       </c>
-      <c r="F8" s="56" t="s">
+      <c r="F8" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="58" t="s">
+      <c r="G8" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="56" t="s">
+      <c r="H8" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="56" t="s">
+      <c r="I8" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J8" s="56" t="s">
+      <c r="J8" s="54" t="s">
         <v>35</v>
       </c>
       <c r="K8" s="46" t="s">
@@ -4122,71 +4122,71 @@
         <v>37</v>
       </c>
       <c r="N8" s="42"/>
-      <c r="O8" s="56" t="s">
+      <c r="O8" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P8" s="56" t="s">
+      <c r="P8" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q8" s="59"/>
+      <c r="Q8" s="57"/>
       <c r="R8" s="45">
         <v>44926</v>
       </c>
-      <c r="S8" s="60">
+      <c r="S8" s="58">
         <v>45291</v>
       </c>
-      <c r="T8" s="57" t="s">
+      <c r="T8" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U8" s="61" t="s">
+      <c r="U8" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V8" s="62" t="s">
+      <c r="V8" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W8" s="56"/>
-      <c r="X8" s="56" t="s">
+      <c r="W8" s="54"/>
+      <c r="X8" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y8" s="56" t="s">
+      <c r="Y8" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z8" s="56" t="s">
+      <c r="Z8" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA8" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:27">
-      <c r="A9" s="56" t="s">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A9" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="57" t="s">
+      <c r="C9" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="57" t="s">
+      <c r="D9" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="E9" s="57">
+      <c r="E9" s="55">
         <v>239867549</v>
       </c>
-      <c r="F9" s="56" t="s">
+      <c r="F9" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="58" t="s">
+      <c r="G9" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="56" t="s">
+      <c r="H9" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="56" t="s">
+      <c r="I9" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="56" t="s">
+      <c r="J9" s="54" t="s">
         <v>35</v>
       </c>
       <c r="K9" s="46" t="s">
@@ -4199,74 +4199,74 @@
         <v>37</v>
       </c>
       <c r="N9" s="42"/>
-      <c r="O9" s="56" t="s">
+      <c r="O9" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="56" t="s">
+      <c r="P9" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="59"/>
+      <c r="Q9" s="57"/>
       <c r="R9" s="45">
         <v>44926</v>
       </c>
-      <c r="S9" s="60">
+      <c r="S9" s="58">
         <v>45291</v>
       </c>
-      <c r="T9" s="57" t="s">
+      <c r="T9" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U9" s="61" t="s">
+      <c r="U9" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V9" s="62" t="s">
+      <c r="V9" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W9" s="56"/>
-      <c r="X9" s="56" t="s">
+      <c r="W9" s="54"/>
+      <c r="X9" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y9" s="56" t="s">
+      <c r="Y9" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z9" s="56" t="s">
+      <c r="Z9" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA9" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:27">
-      <c r="A10" s="56" t="s">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A10" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="57" t="s">
+      <c r="C10" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="57" t="s">
+      <c r="D10" s="55" t="s">
         <v>77</v>
       </c>
-      <c r="E10" s="57">
+      <c r="E10" s="55">
         <v>5247334166</v>
       </c>
-      <c r="F10" s="56" t="s">
+      <c r="F10" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="58" t="s">
+      <c r="G10" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="56" t="s">
+      <c r="H10" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I10" s="56" t="s">
+      <c r="I10" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="56" t="s">
+      <c r="J10" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K10" s="57" t="s">
+      <c r="K10" s="55" t="s">
         <v>78</v>
       </c>
       <c r="L10" s="41" t="s">
@@ -4276,71 +4276,71 @@
         <v>37</v>
       </c>
       <c r="N10" s="42"/>
-      <c r="O10" s="56" t="s">
+      <c r="O10" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P10" s="56" t="s">
+      <c r="P10" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q10" s="59"/>
+      <c r="Q10" s="57"/>
       <c r="R10" s="45">
         <v>44926</v>
       </c>
-      <c r="S10" s="60">
+      <c r="S10" s="58">
         <v>45291</v>
       </c>
-      <c r="T10" s="57" t="s">
+      <c r="T10" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="U10" s="61" t="s">
+      <c r="U10" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V10" s="62" t="s">
+      <c r="V10" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="W10" s="56"/>
-      <c r="X10" s="56" t="s">
+      <c r="W10" s="54"/>
+      <c r="X10" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y10" s="56" t="s">
+      <c r="Y10" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z10" s="56" t="s">
+      <c r="Z10" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:27">
-      <c r="A11" s="56" t="s">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A11" s="54" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="56" t="s">
+      <c r="B11" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="57" t="s">
+      <c r="C11" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="57" t="s">
+      <c r="D11" s="55" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="57">
+      <c r="E11" s="55">
         <v>239867704</v>
       </c>
-      <c r="F11" s="56" t="s">
+      <c r="F11" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="58" t="s">
+      <c r="G11" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="56" t="s">
+      <c r="H11" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I11" s="56" t="s">
+      <c r="I11" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="56" t="s">
+      <c r="J11" s="54" t="s">
         <v>35</v>
       </c>
       <c r="K11" s="46" t="s">
@@ -4353,71 +4353,71 @@
         <v>37</v>
       </c>
       <c r="N11" s="42"/>
-      <c r="O11" s="56" t="s">
+      <c r="O11" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P11" s="56" t="s">
+      <c r="P11" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q11" s="59"/>
+      <c r="Q11" s="57"/>
       <c r="R11" s="45">
         <v>44926</v>
       </c>
-      <c r="S11" s="60">
+      <c r="S11" s="58">
         <v>45291</v>
       </c>
-      <c r="T11" s="57" t="s">
+      <c r="T11" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U11" s="61" t="s">
+      <c r="U11" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V11" s="62" t="s">
+      <c r="V11" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W11" s="56"/>
-      <c r="X11" s="56" t="s">
+      <c r="W11" s="54"/>
+      <c r="X11" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y11" s="56" t="s">
+      <c r="Y11" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z11" s="56" t="s">
+      <c r="Z11" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:27">
-      <c r="A12" s="56" t="s">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A12" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="56" t="s">
+      <c r="B12" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="D12" s="57" t="s">
+      <c r="D12" s="55" t="s">
         <v>83</v>
       </c>
-      <c r="E12" s="57">
+      <c r="E12" s="55">
         <v>124624873</v>
       </c>
-      <c r="F12" s="56" t="s">
+      <c r="F12" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="58" t="s">
+      <c r="G12" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="56" t="s">
+      <c r="H12" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I12" s="56" t="s">
+      <c r="I12" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J12" s="56" t="s">
+      <c r="J12" s="54" t="s">
         <v>35</v>
       </c>
       <c r="K12" s="46" t="s">
@@ -4430,69 +4430,69 @@
         <v>37</v>
       </c>
       <c r="N12" s="42"/>
-      <c r="O12" s="56" t="s">
+      <c r="O12" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P12" s="56" t="s">
+      <c r="P12" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q12" s="59"/>
+      <c r="Q12" s="57"/>
       <c r="R12" s="45">
         <v>44926</v>
       </c>
-      <c r="S12" s="60">
+      <c r="S12" s="58">
         <v>45291</v>
       </c>
-      <c r="T12" s="57" t="s">
+      <c r="T12" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U12" s="61" t="s">
+      <c r="U12" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V12" s="62" t="s">
+      <c r="V12" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W12" s="56"/>
-      <c r="X12" s="56" t="s">
+      <c r="W12" s="54"/>
+      <c r="X12" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y12" s="56" t="s">
+      <c r="Y12" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z12" s="56" t="s">
+      <c r="Z12" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:27">
-      <c r="A13" s="56" t="s">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A13" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="B13" s="56" t="s">
+      <c r="B13" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="57" t="s">
+      <c r="C13" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="57" t="s">
+      <c r="D13" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="E13" s="63"/>
-      <c r="F13" s="56" t="s">
+      <c r="E13" s="61"/>
+      <c r="F13" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="58" t="s">
+      <c r="G13" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H13" s="56" t="s">
+      <c r="H13" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I13" s="56" t="s">
+      <c r="I13" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J13" s="56" t="s">
+      <c r="J13" s="54" t="s">
         <v>35</v>
       </c>
       <c r="K13" s="46" t="s">
@@ -4505,67 +4505,67 @@
         <v>37</v>
       </c>
       <c r="N13" s="42"/>
-      <c r="O13" s="56" t="s">
+      <c r="O13" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P13" s="56" t="s">
+      <c r="P13" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q13" s="59"/>
+      <c r="Q13" s="57"/>
       <c r="R13" s="45">
         <v>44926</v>
       </c>
-      <c r="S13" s="60">
+      <c r="S13" s="58">
         <v>45291</v>
       </c>
-      <c r="T13" s="63"/>
-      <c r="U13" s="61" t="s">
+      <c r="T13" s="61"/>
+      <c r="U13" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V13" s="62" t="s">
+      <c r="V13" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="W13" s="56"/>
-      <c r="X13" s="56" t="s">
+      <c r="W13" s="54"/>
+      <c r="X13" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y13" s="56" t="s">
+      <c r="Y13" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z13" s="56" t="s">
+      <c r="Z13" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA13" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:27">
-      <c r="A14" s="56" t="s">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A14" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="B14" s="56" t="s">
+      <c r="B14" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="57" t="s">
+      <c r="C14" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="D14" s="57" t="s">
+      <c r="D14" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="E14" s="63"/>
-      <c r="F14" s="56" t="s">
+      <c r="E14" s="61"/>
+      <c r="F14" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="58" t="s">
+      <c r="G14" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="56" t="s">
+      <c r="H14" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="56" t="s">
+      <c r="I14" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J14" s="56" t="s">
+      <c r="J14" s="54" t="s">
         <v>35</v>
       </c>
       <c r="K14" s="46" t="s">
@@ -4578,69 +4578,69 @@
         <v>37</v>
       </c>
       <c r="N14" s="42"/>
-      <c r="O14" s="56" t="s">
+      <c r="O14" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P14" s="56" t="s">
+      <c r="P14" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q14" s="59"/>
+      <c r="Q14" s="57"/>
       <c r="R14" s="45">
         <v>44926</v>
       </c>
-      <c r="S14" s="60">
+      <c r="S14" s="58">
         <v>45291</v>
       </c>
-      <c r="T14" s="63"/>
-      <c r="U14" s="61" t="s">
+      <c r="T14" s="61"/>
+      <c r="U14" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V14" s="62" t="s">
+      <c r="V14" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="W14" s="56"/>
-      <c r="X14" s="56" t="s">
+      <c r="W14" s="54"/>
+      <c r="X14" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y14" s="56" t="s">
+      <c r="Y14" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z14" s="56" t="s">
+      <c r="Z14" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:27">
-      <c r="A15" s="56" t="s">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A15" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="B15" s="56" t="s">
+      <c r="B15" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="57" t="s">
+      <c r="C15" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="57" t="s">
+      <c r="D15" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="E15" s="57">
+      <c r="E15" s="55">
         <v>304449708</v>
       </c>
-      <c r="F15" s="56" t="s">
+      <c r="F15" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="58" t="s">
+      <c r="G15" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="56" t="s">
+      <c r="H15" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I15" s="56" t="s">
+      <c r="I15" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J15" s="56" t="s">
+      <c r="J15" s="54" t="s">
         <v>35</v>
       </c>
       <c r="K15" s="46" t="s">
@@ -4653,74 +4653,74 @@
         <v>37</v>
       </c>
       <c r="N15" s="42"/>
-      <c r="O15" s="56" t="s">
+      <c r="O15" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P15" s="56" t="s">
+      <c r="P15" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q15" s="59"/>
+      <c r="Q15" s="57"/>
       <c r="R15" s="45">
         <v>44926</v>
       </c>
-      <c r="S15" s="60">
+      <c r="S15" s="58">
         <v>45291</v>
       </c>
-      <c r="T15" s="57" t="s">
+      <c r="T15" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U15" s="61" t="s">
+      <c r="U15" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V15" s="62" t="s">
+      <c r="V15" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W15" s="56"/>
-      <c r="X15" s="56" t="s">
+      <c r="W15" s="54"/>
+      <c r="X15" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y15" s="56" t="s">
+      <c r="Y15" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z15" s="56" t="s">
+      <c r="Z15" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA15" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:27">
-      <c r="A16" s="56" t="s">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A16" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="B16" s="56" t="s">
+      <c r="B16" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="57" t="s">
+      <c r="C16" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="57" t="s">
+      <c r="D16" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="E16" s="57">
+      <c r="E16" s="55">
         <v>362082471</v>
       </c>
-      <c r="F16" s="56" t="s">
+      <c r="F16" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G16" s="58" t="s">
+      <c r="G16" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="56" t="s">
+      <c r="H16" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I16" s="56" t="s">
+      <c r="I16" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J16" s="56" t="s">
+      <c r="J16" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K16" s="64">
+      <c r="K16" s="62">
         <v>192168254101</v>
       </c>
       <c r="L16" s="41" t="s">
@@ -4730,47 +4730,47 @@
         <v>37</v>
       </c>
       <c r="N16" s="42"/>
-      <c r="O16" s="56" t="s">
+      <c r="O16" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P16" s="56" t="s">
+      <c r="P16" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q16" s="59"/>
+      <c r="Q16" s="57"/>
       <c r="R16" s="45">
         <v>44926</v>
       </c>
-      <c r="S16" s="60">
+      <c r="S16" s="58">
         <v>45291</v>
       </c>
-      <c r="T16" s="57" t="s">
+      <c r="T16" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U16" s="61" t="s">
+      <c r="U16" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V16" s="62" t="s">
+      <c r="V16" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W16" s="56"/>
-      <c r="X16" s="56" t="s">
+      <c r="W16" s="54"/>
+      <c r="X16" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y16" s="56" t="s">
+      <c r="Y16" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z16" s="56" t="s">
+      <c r="Z16" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA16" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:27">
-      <c r="A17" s="56" t="s">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A17" s="54" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="54" t="s">
         <v>47</v>
       </c>
       <c r="C17" s="43" t="s">
@@ -4780,19 +4780,19 @@
         <v>98</v>
       </c>
       <c r="E17" s="47"/>
-      <c r="F17" s="56" t="s">
+      <c r="F17" s="54" t="s">
         <v>31</v>
       </c>
       <c r="G17" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="H17" s="56" t="s">
+      <c r="H17" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I17" s="56" t="s">
+      <c r="I17" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J17" s="56" t="s">
+      <c r="J17" s="54" t="s">
         <v>35</v>
       </c>
       <c r="K17" s="49">
@@ -4805,45 +4805,45 @@
         <v>99</v>
       </c>
       <c r="N17" s="42"/>
-      <c r="O17" s="56" t="s">
+      <c r="O17" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P17" s="56" t="s">
+      <c r="P17" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q17" s="59"/>
+      <c r="Q17" s="57"/>
       <c r="R17" s="45">
         <v>44926</v>
       </c>
-      <c r="S17" s="60">
+      <c r="S17" s="58">
         <v>45291</v>
       </c>
       <c r="T17" s="50"/>
-      <c r="U17" s="61" t="s">
+      <c r="U17" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V17" s="62" t="s">
+      <c r="V17" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W17" s="56"/>
-      <c r="X17" s="56" t="s">
+      <c r="W17" s="54"/>
+      <c r="X17" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y17" s="56" t="s">
+      <c r="Y17" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="Z17" s="56" t="s">
+      <c r="Z17" s="54" t="s">
         <v>101</v>
       </c>
       <c r="AA17" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:27">
-      <c r="A18" s="56" t="s">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A18" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="B18" s="56" t="s">
+      <c r="B18" s="54" t="s">
         <v>47</v>
       </c>
       <c r="C18" s="43" t="s">
@@ -4853,19 +4853,19 @@
         <v>104</v>
       </c>
       <c r="E18" s="47"/>
-      <c r="F18" s="56" t="s">
+      <c r="F18" s="54" t="s">
         <v>31</v>
       </c>
       <c r="G18" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="H18" s="56" t="s">
+      <c r="H18" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I18" s="56" t="s">
+      <c r="I18" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J18" s="56" t="s">
+      <c r="J18" s="54" t="s">
         <v>35</v>
       </c>
       <c r="K18" s="49">
@@ -4878,45 +4878,45 @@
         <v>99</v>
       </c>
       <c r="N18" s="42"/>
-      <c r="O18" s="56" t="s">
+      <c r="O18" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P18" s="56" t="s">
+      <c r="P18" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q18" s="59"/>
+      <c r="Q18" s="57"/>
       <c r="R18" s="45">
         <v>44926</v>
       </c>
-      <c r="S18" s="60">
+      <c r="S18" s="58">
         <v>45291</v>
       </c>
       <c r="T18" s="50"/>
-      <c r="U18" s="61" t="s">
+      <c r="U18" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V18" s="62" t="s">
+      <c r="V18" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W18" s="56"/>
-      <c r="X18" s="56" t="s">
+      <c r="W18" s="54"/>
+      <c r="X18" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y18" s="56" t="s">
+      <c r="Y18" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="Z18" s="56" t="s">
+      <c r="Z18" s="54" t="s">
         <v>101</v>
       </c>
       <c r="AA18" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:27">
-      <c r="A19" s="56" t="s">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A19" s="54" t="s">
         <v>105</v>
       </c>
-      <c r="B19" s="56" t="s">
+      <c r="B19" s="54" t="s">
         <v>47</v>
       </c>
       <c r="C19" s="51" t="s">
@@ -4925,20 +4925,20 @@
       <c r="D19" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="E19" s="57"/>
-      <c r="F19" s="56" t="s">
+      <c r="E19" s="55"/>
+      <c r="F19" s="54" t="s">
         <v>31</v>
       </c>
       <c r="G19" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="H19" s="56" t="s">
+      <c r="H19" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I19" s="56" t="s">
+      <c r="I19" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J19" s="56" t="s">
+      <c r="J19" s="54" t="s">
         <v>35</v>
       </c>
       <c r="K19" s="44">
@@ -4951,67 +4951,67 @@
         <v>99</v>
       </c>
       <c r="N19" s="42"/>
-      <c r="O19" s="56" t="s">
+      <c r="O19" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P19" s="56" t="s">
+      <c r="P19" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q19" s="59"/>
+      <c r="Q19" s="57"/>
       <c r="R19" s="45">
         <v>44926</v>
       </c>
-      <c r="S19" s="60">
+      <c r="S19" s="58">
         <v>45291</v>
       </c>
       <c r="T19" s="50"/>
-      <c r="U19" s="61" t="s">
+      <c r="U19" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V19" s="62" t="s">
+      <c r="V19" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W19" s="56"/>
-      <c r="X19" s="56" t="s">
+      <c r="W19" s="54"/>
+      <c r="X19" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y19" s="56" t="s">
+      <c r="Y19" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="Z19" s="56" t="s">
+      <c r="Z19" s="54" t="s">
         <v>101</v>
       </c>
       <c r="AA19" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:27">
-      <c r="A20" s="56" t="s">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A20" s="54" t="s">
         <v>108</v>
       </c>
-      <c r="B20" s="56" t="s">
+      <c r="B20" s="54" t="s">
         <v>47</v>
       </c>
       <c r="C20" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="D20" s="61" t="s">
+      <c r="D20" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="E20" s="57"/>
-      <c r="F20" s="56" t="s">
+      <c r="E20" s="55"/>
+      <c r="F20" s="54" t="s">
         <v>31</v>
       </c>
       <c r="G20" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="56" t="s">
+      <c r="H20" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I20" s="56" t="s">
+      <c r="I20" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J20" s="56" t="s">
+      <c r="J20" s="54" t="s">
         <v>35</v>
       </c>
       <c r="K20" s="52">
@@ -5024,72 +5024,72 @@
         <v>99</v>
       </c>
       <c r="N20" s="42"/>
-      <c r="O20" s="56" t="s">
+      <c r="O20" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P20" s="56" t="s">
+      <c r="P20" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q20" s="59"/>
+      <c r="Q20" s="57"/>
       <c r="R20" s="45">
         <v>44926</v>
       </c>
-      <c r="S20" s="60">
+      <c r="S20" s="58">
         <v>45291</v>
       </c>
       <c r="T20" s="50"/>
-      <c r="U20" s="61" t="s">
+      <c r="U20" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V20" s="62" t="s">
+      <c r="V20" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W20" s="56"/>
-      <c r="X20" s="56" t="s">
+      <c r="W20" s="54"/>
+      <c r="X20" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y20" s="56" t="s">
+      <c r="Y20" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="Z20" s="56" t="s">
+      <c r="Z20" s="54" t="s">
         <v>101</v>
       </c>
       <c r="AA20" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:27">
-      <c r="A21" s="56" t="s">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A21" s="54" t="s">
         <v>110</v>
       </c>
-      <c r="B21" s="56" t="s">
+      <c r="B21" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="57" t="s">
+      <c r="C21" s="55" t="s">
         <v>111</v>
       </c>
-      <c r="D21" s="57" t="s">
+      <c r="D21" s="55" t="s">
         <v>112</v>
       </c>
-      <c r="E21" s="57">
+      <c r="E21" s="55">
         <v>393473022</v>
       </c>
-      <c r="F21" s="56" t="s">
+      <c r="F21" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G21" s="58" t="s">
+      <c r="G21" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H21" s="56" t="s">
+      <c r="H21" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I21" s="56" t="s">
+      <c r="I21" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J21" s="56" t="s">
+      <c r="J21" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K21" s="64">
+      <c r="K21" s="62">
         <v>192168254121</v>
       </c>
       <c r="L21" s="41" t="s">
@@ -5099,74 +5099,74 @@
         <v>37</v>
       </c>
       <c r="N21" s="42"/>
-      <c r="O21" s="56" t="s">
+      <c r="O21" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P21" s="56" t="s">
+      <c r="P21" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q21" s="59"/>
+      <c r="Q21" s="57"/>
       <c r="R21" s="45">
         <v>44926</v>
       </c>
-      <c r="S21" s="60">
+      <c r="S21" s="58">
         <v>45291</v>
       </c>
-      <c r="T21" s="57" t="s">
+      <c r="T21" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U21" s="61" t="s">
+      <c r="U21" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V21" s="62" t="s">
+      <c r="V21" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W21" s="56"/>
-      <c r="X21" s="56" t="s">
+      <c r="W21" s="54"/>
+      <c r="X21" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y21" s="56" t="s">
+      <c r="Y21" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z21" s="56" t="s">
+      <c r="Z21" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:27">
-      <c r="A22" s="65" t="s">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A22" s="63" t="s">
         <v>113</v>
       </c>
-      <c r="B22" s="56" t="s">
+      <c r="B22" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="57" t="s">
+      <c r="C22" s="55" t="s">
         <v>114</v>
       </c>
-      <c r="D22" s="57" t="s">
+      <c r="D22" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="E22" s="57">
+      <c r="E22" s="55">
         <v>849464899</v>
       </c>
-      <c r="F22" s="56" t="s">
+      <c r="F22" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G22" s="58" t="s">
+      <c r="G22" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H22" s="56" t="s">
+      <c r="H22" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I22" s="56" t="s">
+      <c r="I22" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J22" s="56" t="s">
+      <c r="J22" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K22" s="64">
+      <c r="K22" s="62">
         <v>192168254122</v>
       </c>
       <c r="L22" s="41" t="s">
@@ -5176,74 +5176,74 @@
         <v>37</v>
       </c>
       <c r="N22" s="42"/>
-      <c r="O22" s="56" t="s">
+      <c r="O22" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P22" s="56" t="s">
+      <c r="P22" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q22" s="59"/>
+      <c r="Q22" s="57"/>
       <c r="R22" s="45">
         <v>44926</v>
       </c>
-      <c r="S22" s="60">
+      <c r="S22" s="58">
         <v>45291</v>
       </c>
-      <c r="T22" s="57" t="s">
+      <c r="T22" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U22" s="61" t="s">
+      <c r="U22" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V22" s="62" t="s">
+      <c r="V22" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W22" s="56"/>
-      <c r="X22" s="56" t="s">
+      <c r="W22" s="54"/>
+      <c r="X22" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y22" s="56" t="s">
+      <c r="Y22" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z22" s="56" t="s">
+      <c r="Z22" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:27">
-      <c r="A23" s="56" t="s">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A23" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="B23" s="56" t="s">
+      <c r="B23" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="57" t="s">
+      <c r="C23" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="D23" s="57" t="s">
+      <c r="D23" s="55" t="s">
         <v>117</v>
       </c>
-      <c r="E23" s="57">
+      <c r="E23" s="55">
         <v>822460962</v>
       </c>
-      <c r="F23" s="56" t="s">
+      <c r="F23" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G23" s="58" t="s">
+      <c r="G23" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="56" t="s">
+      <c r="H23" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I23" s="56" t="s">
+      <c r="I23" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J23" s="56" t="s">
+      <c r="J23" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K23" s="64">
+      <c r="K23" s="62">
         <v>192168254123</v>
       </c>
       <c r="L23" s="41" t="s">
@@ -5253,72 +5253,72 @@
         <v>37</v>
       </c>
       <c r="N23" s="42"/>
-      <c r="O23" s="56" t="s">
+      <c r="O23" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P23" s="56" t="s">
+      <c r="P23" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q23" s="59"/>
+      <c r="Q23" s="57"/>
       <c r="R23" s="45">
         <v>44926</v>
       </c>
-      <c r="S23" s="60">
+      <c r="S23" s="58">
         <v>45291</v>
       </c>
-      <c r="T23" s="57" t="s">
+      <c r="T23" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U23" s="61" t="s">
+      <c r="U23" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V23" s="62" t="s">
+      <c r="V23" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W23" s="56"/>
-      <c r="X23" s="56" t="s">
+      <c r="W23" s="54"/>
+      <c r="X23" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y23" s="56" t="s">
+      <c r="Y23" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z23" s="56" t="s">
+      <c r="Z23" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA23" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:27">
-      <c r="A24" s="66" t="s">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A24" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="B24" s="66" t="s">
+      <c r="B24" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="67" t="s">
+      <c r="C24" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="D24" s="67" t="s">
+      <c r="D24" s="65" t="s">
         <v>119</v>
       </c>
-      <c r="E24" s="63"/>
-      <c r="F24" s="56" t="s">
+      <c r="E24" s="61"/>
+      <c r="F24" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G24" s="58" t="s">
+      <c r="G24" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H24" s="56" t="s">
+      <c r="H24" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I24" s="56" t="s">
+      <c r="I24" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J24" s="56" t="s">
+      <c r="J24" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K24" s="64">
+      <c r="K24" s="62">
         <v>192168254124</v>
       </c>
       <c r="L24" s="41" t="s">
@@ -5328,70 +5328,70 @@
         <v>37</v>
       </c>
       <c r="N24" s="42"/>
-      <c r="O24" s="56" t="s">
+      <c r="O24" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P24" s="56" t="s">
+      <c r="P24" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q24" s="59"/>
+      <c r="Q24" s="57"/>
       <c r="R24" s="45">
         <v>44926</v>
       </c>
-      <c r="S24" s="60">
+      <c r="S24" s="58">
         <v>45291</v>
       </c>
-      <c r="T24" s="63"/>
-      <c r="U24" s="61" t="s">
+      <c r="T24" s="61"/>
+      <c r="U24" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V24" s="62" t="s">
+      <c r="V24" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W24" s="56"/>
-      <c r="X24" s="56" t="s">
+      <c r="W24" s="54"/>
+      <c r="X24" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y24" s="56" t="s">
+      <c r="Y24" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z24" s="56" t="s">
+      <c r="Z24" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA24" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:27">
-      <c r="A25" s="66" t="s">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A25" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="B25" s="66" t="s">
+      <c r="B25" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="67" t="s">
+      <c r="C25" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="67" t="s">
+      <c r="D25" s="65" t="s">
         <v>120</v>
       </c>
-      <c r="E25" s="63"/>
-      <c r="F25" s="56" t="s">
+      <c r="E25" s="61"/>
+      <c r="F25" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G25" s="58" t="s">
+      <c r="G25" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H25" s="56" t="s">
+      <c r="H25" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I25" s="56" t="s">
+      <c r="I25" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J25" s="56" t="s">
+      <c r="J25" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K25" s="64">
+      <c r="K25" s="62">
         <v>192168254124</v>
       </c>
       <c r="L25" s="41" t="s">
@@ -5401,72 +5401,72 @@
         <v>37</v>
       </c>
       <c r="N25" s="42"/>
-      <c r="O25" s="56" t="s">
+      <c r="O25" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P25" s="56" t="s">
+      <c r="P25" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q25" s="59"/>
+      <c r="Q25" s="57"/>
       <c r="R25" s="45">
         <v>44926</v>
       </c>
-      <c r="S25" s="60">
+      <c r="S25" s="58">
         <v>45291</v>
       </c>
-      <c r="T25" s="63"/>
-      <c r="U25" s="61" t="s">
+      <c r="T25" s="61"/>
+      <c r="U25" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V25" s="62" t="s">
+      <c r="V25" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W25" s="56"/>
-      <c r="X25" s="56" t="s">
+      <c r="W25" s="54"/>
+      <c r="X25" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y25" s="56" t="s">
+      <c r="Y25" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z25" s="56" t="s">
+      <c r="Z25" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:27">
-      <c r="A26" s="56" t="s">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A26" s="54" t="s">
         <v>121</v>
       </c>
-      <c r="B26" s="56" t="s">
+      <c r="B26" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="57" t="s">
+      <c r="C26" s="55" t="s">
         <v>122</v>
       </c>
-      <c r="D26" s="57" t="s">
+      <c r="D26" s="55" t="s">
         <v>123</v>
       </c>
-      <c r="E26" s="57">
+      <c r="E26" s="55">
         <v>5290525327</v>
       </c>
-      <c r="F26" s="56" t="s">
+      <c r="F26" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G26" s="58" t="s">
+      <c r="G26" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H26" s="56" t="s">
+      <c r="H26" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I26" s="56" t="s">
+      <c r="I26" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J26" s="56" t="s">
+      <c r="J26" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K26" s="64">
+      <c r="K26" s="62">
         <v>192168254127</v>
       </c>
       <c r="L26" s="41" t="s">
@@ -5476,74 +5476,74 @@
         <v>37</v>
       </c>
       <c r="N26" s="42"/>
-      <c r="O26" s="56" t="s">
+      <c r="O26" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P26" s="56" t="s">
+      <c r="P26" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q26" s="59"/>
+      <c r="Q26" s="57"/>
       <c r="R26" s="45">
         <v>44926</v>
       </c>
-      <c r="S26" s="60">
+      <c r="S26" s="58">
         <v>45291</v>
       </c>
-      <c r="T26" s="57" t="s">
+      <c r="T26" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U26" s="61" t="s">
+      <c r="U26" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V26" s="62" t="s">
+      <c r="V26" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="W26" s="56"/>
-      <c r="X26" s="56" t="s">
+      <c r="W26" s="54"/>
+      <c r="X26" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y26" s="56" t="s">
+      <c r="Y26" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z26" s="56" t="s">
+      <c r="Z26" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA26" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:27">
-      <c r="A27" s="56" t="s">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A27" s="54" t="s">
         <v>124</v>
       </c>
-      <c r="B27" s="56" t="s">
+      <c r="B27" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="57" t="s">
+      <c r="C27" s="55" t="s">
         <v>125</v>
       </c>
-      <c r="D27" s="57" t="s">
+      <c r="D27" s="55" t="s">
         <v>126</v>
       </c>
-      <c r="E27" s="57">
+      <c r="E27" s="55">
         <v>216046012</v>
       </c>
-      <c r="F27" s="56" t="s">
+      <c r="F27" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G27" s="58" t="s">
+      <c r="G27" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H27" s="56" t="s">
+      <c r="H27" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I27" s="56" t="s">
+      <c r="I27" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J27" s="56" t="s">
+      <c r="J27" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K27" s="68">
+      <c r="K27" s="66">
         <v>192168254249</v>
       </c>
       <c r="L27" s="41" t="s">
@@ -5553,72 +5553,72 @@
         <v>37</v>
       </c>
       <c r="N27" s="42"/>
-      <c r="O27" s="56" t="s">
+      <c r="O27" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P27" s="56" t="s">
+      <c r="P27" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q27" s="59"/>
+      <c r="Q27" s="57"/>
       <c r="R27" s="45">
         <v>44926</v>
       </c>
-      <c r="S27" s="60">
+      <c r="S27" s="58">
         <v>45291</v>
       </c>
-      <c r="T27" s="57" t="s">
+      <c r="T27" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U27" s="61" t="s">
+      <c r="U27" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V27" s="62" t="s">
+      <c r="V27" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W27" s="56"/>
-      <c r="X27" s="56" t="s">
+      <c r="W27" s="54"/>
+      <c r="X27" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="Y27" s="56" t="s">
+      <c r="Y27" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z27" s="56" t="s">
+      <c r="Z27" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA27" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:27">
-      <c r="A28" s="56" t="s">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A28" s="54" t="s">
         <v>124</v>
       </c>
-      <c r="B28" s="56" t="s">
+      <c r="B28" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C28" s="57" t="s">
+      <c r="C28" s="55" t="s">
         <v>128</v>
       </c>
       <c r="D28" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="E28" s="63"/>
-      <c r="F28" s="56" t="s">
+      <c r="E28" s="61"/>
+      <c r="F28" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G28" s="58" t="s">
+      <c r="G28" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H28" s="56" t="s">
+      <c r="H28" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I28" s="56" t="s">
+      <c r="I28" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J28" s="56" t="s">
+      <c r="J28" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K28" s="68">
+      <c r="K28" s="66">
         <v>192168254249</v>
       </c>
       <c r="L28" s="41" t="s">
@@ -5628,74 +5628,74 @@
         <v>37</v>
       </c>
       <c r="N28" s="42"/>
-      <c r="O28" s="56" t="s">
+      <c r="O28" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P28" s="56" t="s">
+      <c r="P28" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q28" s="59"/>
+      <c r="Q28" s="57"/>
       <c r="R28" s="45">
         <v>44926</v>
       </c>
-      <c r="S28" s="60">
+      <c r="S28" s="58">
         <v>45291</v>
       </c>
-      <c r="T28" s="57" t="s">
+      <c r="T28" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U28" s="61" t="s">
+      <c r="U28" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V28" s="62" t="s">
+      <c r="V28" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W28" s="56"/>
-      <c r="X28" s="56" t="s">
+      <c r="W28" s="54"/>
+      <c r="X28" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="Y28" s="56" t="s">
+      <c r="Y28" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z28" s="56" t="s">
+      <c r="Z28" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA28" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:27">
-      <c r="A29" s="56" t="s">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A29" s="54" t="s">
         <v>124</v>
       </c>
-      <c r="B29" s="56" t="s">
+      <c r="B29" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="57" t="s">
+      <c r="C29" s="55" t="s">
         <v>125</v>
       </c>
-      <c r="D29" s="57" t="s">
+      <c r="D29" s="55" t="s">
         <v>130</v>
       </c>
-      <c r="E29" s="57">
+      <c r="E29" s="55">
         <v>238890038</v>
       </c>
-      <c r="F29" s="56" t="s">
+      <c r="F29" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G29" s="58" t="s">
+      <c r="G29" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H29" s="56" t="s">
+      <c r="H29" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I29" s="56" t="s">
+      <c r="I29" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J29" s="56" t="s">
+      <c r="J29" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K29" s="68">
+      <c r="K29" s="66">
         <v>192168254249</v>
       </c>
       <c r="L29" s="41" t="s">
@@ -5705,74 +5705,74 @@
         <v>37</v>
       </c>
       <c r="N29" s="42"/>
-      <c r="O29" s="56" t="s">
+      <c r="O29" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P29" s="56" t="s">
+      <c r="P29" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q29" s="59"/>
+      <c r="Q29" s="57"/>
       <c r="R29" s="45">
         <v>44926</v>
       </c>
-      <c r="S29" s="60">
+      <c r="S29" s="58">
         <v>45291</v>
       </c>
-      <c r="T29" s="57" t="s">
+      <c r="T29" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U29" s="61" t="s">
+      <c r="U29" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V29" s="62" t="s">
+      <c r="V29" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W29" s="56"/>
-      <c r="X29" s="56" t="s">
+      <c r="W29" s="54"/>
+      <c r="X29" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="Y29" s="56" t="s">
+      <c r="Y29" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z29" s="56" t="s">
+      <c r="Z29" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA29" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:27">
-      <c r="A30" s="56" t="s">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A30" s="54" t="s">
         <v>124</v>
       </c>
-      <c r="B30" s="56" t="s">
+      <c r="B30" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="57" t="s">
+      <c r="C30" s="55" t="s">
         <v>125</v>
       </c>
-      <c r="D30" s="57" t="s">
+      <c r="D30" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="E30" s="57">
+      <c r="E30" s="55">
         <v>399846907</v>
       </c>
-      <c r="F30" s="56" t="s">
+      <c r="F30" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G30" s="58" t="s">
+      <c r="G30" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H30" s="56" t="s">
+      <c r="H30" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I30" s="56" t="s">
+      <c r="I30" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J30" s="56" t="s">
+      <c r="J30" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K30" s="68">
+      <c r="K30" s="66">
         <v>192168254249</v>
       </c>
       <c r="L30" s="41" t="s">
@@ -5782,74 +5782,74 @@
         <v>37</v>
       </c>
       <c r="N30" s="42"/>
-      <c r="O30" s="56" t="s">
+      <c r="O30" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P30" s="56" t="s">
+      <c r="P30" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q30" s="59"/>
+      <c r="Q30" s="57"/>
       <c r="R30" s="45">
         <v>44926</v>
       </c>
-      <c r="S30" s="60">
+      <c r="S30" s="58">
         <v>45291</v>
       </c>
-      <c r="T30" s="57" t="s">
+      <c r="T30" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U30" s="61" t="s">
+      <c r="U30" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V30" s="62" t="s">
+      <c r="V30" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W30" s="56"/>
-      <c r="X30" s="56" t="s">
+      <c r="W30" s="54"/>
+      <c r="X30" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="Y30" s="56" t="s">
+      <c r="Y30" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z30" s="56" t="s">
+      <c r="Z30" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA30" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="1:27">
-      <c r="A31" s="56" t="s">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A31" s="54" t="s">
         <v>132</v>
       </c>
-      <c r="B31" s="56" t="s">
+      <c r="B31" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C31" s="57" t="s">
+      <c r="C31" s="55" t="s">
         <v>133</v>
       </c>
-      <c r="D31" s="57" t="s">
+      <c r="D31" s="55" t="s">
         <v>134</v>
       </c>
-      <c r="E31" s="57">
+      <c r="E31" s="55">
         <v>5488763791</v>
       </c>
-      <c r="F31" s="56" t="s">
+      <c r="F31" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G31" s="58" t="s">
+      <c r="G31" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="H31" s="56" t="s">
+      <c r="H31" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I31" s="56" t="s">
+      <c r="I31" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J31" s="56" t="s">
+      <c r="J31" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K31" s="64">
+      <c r="K31" s="62">
         <v>192168254250</v>
       </c>
       <c r="L31" s="41" t="s">
@@ -5859,74 +5859,74 @@
         <v>37</v>
       </c>
       <c r="N31" s="42"/>
-      <c r="O31" s="56" t="s">
+      <c r="O31" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P31" s="56" t="s">
+      <c r="P31" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q31" s="59"/>
+      <c r="Q31" s="57"/>
       <c r="R31" s="45">
         <v>44926</v>
       </c>
-      <c r="S31" s="60">
+      <c r="S31" s="58">
         <v>45291</v>
       </c>
-      <c r="T31" s="57" t="s">
+      <c r="T31" s="55" t="s">
         <v>136</v>
       </c>
-      <c r="U31" s="61" t="s">
+      <c r="U31" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V31" s="62" t="s">
+      <c r="V31" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="W31" s="56"/>
-      <c r="X31" s="56" t="s">
+      <c r="W31" s="54"/>
+      <c r="X31" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="Y31" s="56" t="s">
+      <c r="Y31" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z31" s="56" t="s">
+      <c r="Z31" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA31" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="1:27">
-      <c r="A32" s="56" t="s">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A32" s="54" t="s">
         <v>132</v>
       </c>
-      <c r="B32" s="56" t="s">
+      <c r="B32" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C32" s="57" t="s">
+      <c r="C32" s="55" t="s">
         <v>133</v>
       </c>
-      <c r="D32" s="57" t="s">
+      <c r="D32" s="55" t="s">
         <v>137</v>
       </c>
-      <c r="E32" s="57">
+      <c r="E32" s="55">
         <v>5488763793</v>
       </c>
-      <c r="F32" s="56" t="s">
+      <c r="F32" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G32" s="58" t="s">
+      <c r="G32" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="H32" s="56" t="s">
+      <c r="H32" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I32" s="56" t="s">
+      <c r="I32" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J32" s="56" t="s">
+      <c r="J32" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K32" s="64">
+      <c r="K32" s="62">
         <v>192168254250</v>
       </c>
       <c r="L32" s="41" t="s">
@@ -5936,72 +5936,72 @@
         <v>37</v>
       </c>
       <c r="N32" s="42"/>
-      <c r="O32" s="56" t="s">
+      <c r="O32" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P32" s="56" t="s">
+      <c r="P32" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q32" s="59"/>
+      <c r="Q32" s="57"/>
       <c r="R32" s="45">
         <v>44926</v>
       </c>
-      <c r="S32" s="60">
+      <c r="S32" s="58">
         <v>45291</v>
       </c>
-      <c r="T32" s="57" t="s">
+      <c r="T32" s="55" t="s">
         <v>136</v>
       </c>
-      <c r="U32" s="61" t="s">
+      <c r="U32" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V32" s="62" t="s">
+      <c r="V32" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="W32" s="56"/>
-      <c r="X32" s="56" t="s">
+      <c r="W32" s="54"/>
+      <c r="X32" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="Y32" s="56" t="s">
+      <c r="Y32" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z32" s="56" t="s">
+      <c r="Z32" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA32" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="33" spans="1:27">
-      <c r="A33" s="69" t="s">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A33" s="67" t="s">
         <v>138</v>
       </c>
-      <c r="B33" s="56" t="s">
+      <c r="B33" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="57" t="s">
+      <c r="C33" s="55" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="57" t="s">
+      <c r="D33" s="55" t="s">
         <v>140</v>
       </c>
-      <c r="E33" s="63"/>
-      <c r="F33" s="56" t="s">
+      <c r="E33" s="61"/>
+      <c r="F33" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G33" s="58" t="s">
+      <c r="G33" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="H33" s="56" t="s">
+      <c r="H33" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I33" s="56" t="s">
+      <c r="I33" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J33" s="56" t="s">
+      <c r="J33" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K33" s="57" t="s">
+      <c r="K33" s="55" t="s">
         <v>141</v>
       </c>
       <c r="L33" s="41" t="s">
@@ -6011,72 +6011,72 @@
         <v>37</v>
       </c>
       <c r="N33" s="42"/>
-      <c r="O33" s="56" t="s">
+      <c r="O33" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P33" s="56" t="s">
+      <c r="P33" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q33" s="59"/>
+      <c r="Q33" s="57"/>
       <c r="R33" s="45">
         <v>44926</v>
       </c>
-      <c r="S33" s="60">
+      <c r="S33" s="58">
         <v>45291</v>
       </c>
-      <c r="T33" s="63"/>
-      <c r="U33" s="61" t="s">
+      <c r="T33" s="61"/>
+      <c r="U33" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V33" s="62" t="s">
+      <c r="V33" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="W33" s="56"/>
-      <c r="X33" s="56" t="s">
+      <c r="W33" s="54"/>
+      <c r="X33" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y33" s="56" t="s">
+      <c r="Y33" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z33" s="56" t="s">
+      <c r="Z33" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA33" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="34" spans="1:27">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="B34" s="56" t="s">
+      <c r="B34" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C34" s="57" t="s">
+      <c r="C34" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="D34" s="57" t="s">
+      <c r="D34" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="E34" s="57">
+      <c r="E34" s="55">
         <v>5121963933</v>
       </c>
-      <c r="F34" s="56" t="s">
+      <c r="F34" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G34" s="58" t="s">
+      <c r="G34" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="H34" s="56" t="s">
+      <c r="H34" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I34" s="56" t="s">
+      <c r="I34" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J34" s="56" t="s">
+      <c r="J34" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K34" s="57" t="s">
+      <c r="K34" s="55" t="s">
         <v>144</v>
       </c>
       <c r="L34" s="41" t="s">
@@ -6086,74 +6086,74 @@
         <v>37</v>
       </c>
       <c r="N34" s="42"/>
-      <c r="O34" s="56" t="s">
+      <c r="O34" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P34" s="56" t="s">
+      <c r="P34" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q34" s="59"/>
+      <c r="Q34" s="57"/>
       <c r="R34" s="45">
         <v>44926</v>
       </c>
-      <c r="S34" s="60">
+      <c r="S34" s="58">
         <v>45291</v>
       </c>
-      <c r="T34" s="57" t="s">
+      <c r="T34" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U34" s="61" t="s">
+      <c r="U34" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V34" s="62" t="s">
+      <c r="V34" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W34" s="56"/>
-      <c r="X34" s="56" t="s">
+      <c r="W34" s="54"/>
+      <c r="X34" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y34" s="56" t="s">
+      <c r="Y34" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z34" s="56" t="s">
+      <c r="Z34" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA34" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:27">
-      <c r="A35" s="61" t="s">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A35" s="59" t="s">
         <v>145</v>
       </c>
-      <c r="B35" s="56" t="s">
+      <c r="B35" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="57" t="s">
+      <c r="C35" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="D35" s="57" t="s">
+      <c r="D35" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="E35" s="57">
+      <c r="E35" s="55">
         <v>415611943</v>
       </c>
-      <c r="F35" s="56" t="s">
+      <c r="F35" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G35" s="58" t="s">
+      <c r="G35" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="H35" s="56" t="s">
+      <c r="H35" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I35" s="56" t="s">
+      <c r="I35" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J35" s="56" t="s">
+      <c r="J35" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K35" s="70" t="s">
+      <c r="K35" s="68" t="s">
         <v>147</v>
       </c>
       <c r="L35" s="41" t="s">
@@ -6163,74 +6163,74 @@
         <v>37</v>
       </c>
       <c r="N35" s="42"/>
-      <c r="O35" s="56" t="s">
+      <c r="O35" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P35" s="56" t="s">
+      <c r="P35" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q35" s="59"/>
+      <c r="Q35" s="57"/>
       <c r="R35" s="45">
         <v>44926</v>
       </c>
-      <c r="S35" s="60">
+      <c r="S35" s="58">
         <v>45291</v>
       </c>
-      <c r="T35" s="57" t="s">
+      <c r="T35" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U35" s="61" t="s">
+      <c r="U35" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V35" s="62" t="s">
+      <c r="V35" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W35" s="56"/>
-      <c r="X35" s="56" t="s">
+      <c r="W35" s="54"/>
+      <c r="X35" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y35" s="56" t="s">
+      <c r="Y35" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z35" s="56" t="s">
+      <c r="Z35" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA35" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="36" spans="1:27">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36" s="43" t="s">
         <v>148</v>
       </c>
-      <c r="B36" s="56" t="s">
+      <c r="B36" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C36" s="57" t="s">
+      <c r="C36" s="55" t="s">
         <v>149</v>
       </c>
-      <c r="D36" s="57" t="s">
+      <c r="D36" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="E36" s="57">
+      <c r="E36" s="55">
         <v>1592589150</v>
       </c>
-      <c r="F36" s="56" t="s">
+      <c r="F36" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G36" s="58" t="s">
+      <c r="G36" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="H36" s="56" t="s">
+      <c r="H36" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I36" s="56" t="s">
+      <c r="I36" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J36" s="56" t="s">
+      <c r="J36" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K36" s="57" t="s">
+      <c r="K36" s="55" t="s">
         <v>151</v>
       </c>
       <c r="L36" s="41" t="s">
@@ -6240,74 +6240,74 @@
         <v>37</v>
       </c>
       <c r="N36" s="42"/>
-      <c r="O36" s="56" t="s">
+      <c r="O36" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P36" s="56" t="s">
+      <c r="P36" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q36" s="59"/>
+      <c r="Q36" s="57"/>
       <c r="R36" s="45">
         <v>44926</v>
       </c>
-      <c r="S36" s="60">
+      <c r="S36" s="58">
         <v>45291</v>
       </c>
-      <c r="T36" s="57" t="s">
+      <c r="T36" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U36" s="61" t="s">
+      <c r="U36" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V36" s="62" t="s">
+      <c r="V36" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W36" s="56"/>
-      <c r="X36" s="56" t="s">
+      <c r="W36" s="54"/>
+      <c r="X36" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y36" s="56" t="s">
+      <c r="Y36" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z36" s="56" t="s">
+      <c r="Z36" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA36" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:27">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37" s="43" t="s">
         <v>152</v>
       </c>
-      <c r="B37" s="56" t="s">
+      <c r="B37" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C37" s="57" t="s">
+      <c r="C37" s="55" t="s">
         <v>153</v>
       </c>
-      <c r="D37" s="57" t="s">
+      <c r="D37" s="55" t="s">
         <v>154</v>
       </c>
-      <c r="E37" s="57">
+      <c r="E37" s="55">
         <v>953139227</v>
       </c>
-      <c r="F37" s="56" t="s">
+      <c r="F37" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G37" s="58" t="s">
+      <c r="G37" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="H37" s="56" t="s">
+      <c r="H37" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I37" s="56" t="s">
+      <c r="I37" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J37" s="56" t="s">
+      <c r="J37" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K37" s="57" t="s">
+      <c r="K37" s="55" t="s">
         <v>155</v>
       </c>
       <c r="L37" s="41" t="s">
@@ -6317,74 +6317,74 @@
         <v>37</v>
       </c>
       <c r="N37" s="42"/>
-      <c r="O37" s="56" t="s">
+      <c r="O37" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P37" s="56" t="s">
+      <c r="P37" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q37" s="59"/>
+      <c r="Q37" s="57"/>
       <c r="R37" s="45">
         <v>44926</v>
       </c>
-      <c r="S37" s="60">
+      <c r="S37" s="58">
         <v>45291</v>
       </c>
-      <c r="T37" s="57" t="s">
+      <c r="T37" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U37" s="61" t="s">
+      <c r="U37" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V37" s="62" t="s">
+      <c r="V37" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="W37" s="56"/>
-      <c r="X37" s="56" t="s">
+      <c r="W37" s="54"/>
+      <c r="X37" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y37" s="56" t="s">
+      <c r="Y37" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z37" s="56" t="s">
+      <c r="Z37" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA37" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="1:27">
-      <c r="A38" s="61" t="s">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A38" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="B38" s="56" t="s">
+      <c r="B38" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C38" s="57" t="s">
+      <c r="C38" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="D38" s="57" t="s">
+      <c r="D38" s="55" t="s">
         <v>157</v>
       </c>
-      <c r="E38" s="57">
+      <c r="E38" s="55">
         <v>214948869</v>
       </c>
-      <c r="F38" s="56" t="s">
+      <c r="F38" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G38" s="58" t="s">
+      <c r="G38" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="H38" s="56" t="s">
+      <c r="H38" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I38" s="56" t="s">
+      <c r="I38" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J38" s="56" t="s">
+      <c r="J38" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K38" s="57" t="s">
+      <c r="K38" s="55" t="s">
         <v>158</v>
       </c>
       <c r="L38" s="41" t="s">
@@ -6394,74 +6394,74 @@
         <v>37</v>
       </c>
       <c r="N38" s="42"/>
-      <c r="O38" s="56" t="s">
+      <c r="O38" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P38" s="56" t="s">
+      <c r="P38" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q38" s="59"/>
+      <c r="Q38" s="57"/>
       <c r="R38" s="45">
         <v>44926</v>
       </c>
-      <c r="S38" s="60">
+      <c r="S38" s="58">
         <v>45291</v>
       </c>
-      <c r="T38" s="57" t="s">
+      <c r="T38" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U38" s="61" t="s">
+      <c r="U38" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V38" s="62" t="s">
+      <c r="V38" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W38" s="56"/>
-      <c r="X38" s="56" t="s">
+      <c r="W38" s="54"/>
+      <c r="X38" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y38" s="56" t="s">
+      <c r="Y38" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z38" s="56" t="s">
+      <c r="Z38" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA38" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="1:27">
-      <c r="A39" s="61" t="s">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A39" s="59" t="s">
         <v>159</v>
       </c>
-      <c r="B39" s="56" t="s">
+      <c r="B39" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C39" s="57" t="s">
+      <c r="C39" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="D39" s="57" t="s">
+      <c r="D39" s="55" t="s">
         <v>160</v>
       </c>
-      <c r="E39" s="57">
+      <c r="E39" s="55">
         <v>528241455</v>
       </c>
-      <c r="F39" s="56" t="s">
+      <c r="F39" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G39" s="58" t="s">
+      <c r="G39" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="H39" s="56" t="s">
+      <c r="H39" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I39" s="56" t="s">
+      <c r="I39" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J39" s="56" t="s">
+      <c r="J39" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K39" s="57" t="s">
+      <c r="K39" s="55" t="s">
         <v>161</v>
       </c>
       <c r="L39" s="41" t="s">
@@ -6471,74 +6471,74 @@
         <v>37</v>
       </c>
       <c r="N39" s="42"/>
-      <c r="O39" s="56" t="s">
+      <c r="O39" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P39" s="56" t="s">
+      <c r="P39" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q39" s="59"/>
+      <c r="Q39" s="57"/>
       <c r="R39" s="45">
         <v>44926</v>
       </c>
-      <c r="S39" s="60">
+      <c r="S39" s="58">
         <v>45291</v>
       </c>
-      <c r="T39" s="57" t="s">
+      <c r="T39" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U39" s="61" t="s">
+      <c r="U39" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V39" s="62" t="s">
+      <c r="V39" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="W39" s="56"/>
-      <c r="X39" s="56" t="s">
+      <c r="W39" s="54"/>
+      <c r="X39" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y39" s="56" t="s">
+      <c r="Y39" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z39" s="56" t="s">
+      <c r="Z39" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA39" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="40" spans="1:27">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A40" s="43" t="s">
         <v>162</v>
       </c>
-      <c r="B40" s="56" t="s">
+      <c r="B40" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="57" t="s">
+      <c r="C40" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="D40" s="57" t="s">
+      <c r="D40" s="55" t="s">
         <v>163</v>
       </c>
-      <c r="E40" s="57">
+      <c r="E40" s="55">
         <v>1597613354</v>
       </c>
-      <c r="F40" s="56" t="s">
+      <c r="F40" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G40" s="58" t="s">
+      <c r="G40" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="H40" s="56" t="s">
+      <c r="H40" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I40" s="56" t="s">
+      <c r="I40" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J40" s="56" t="s">
+      <c r="J40" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K40" s="57" t="s">
+      <c r="K40" s="55" t="s">
         <v>164</v>
       </c>
       <c r="L40" s="41" t="s">
@@ -6548,74 +6548,74 @@
         <v>37</v>
       </c>
       <c r="N40" s="42"/>
-      <c r="O40" s="56" t="s">
+      <c r="O40" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P40" s="56" t="s">
+      <c r="P40" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q40" s="59"/>
+      <c r="Q40" s="57"/>
       <c r="R40" s="45">
         <v>44926</v>
       </c>
-      <c r="S40" s="60">
+      <c r="S40" s="58">
         <v>45291</v>
       </c>
-      <c r="T40" s="57" t="s">
+      <c r="T40" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U40" s="61" t="s">
+      <c r="U40" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V40" s="62" t="s">
+      <c r="V40" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="W40" s="56"/>
-      <c r="X40" s="56" t="s">
+      <c r="W40" s="54"/>
+      <c r="X40" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y40" s="56" t="s">
+      <c r="Y40" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z40" s="56" t="s">
+      <c r="Z40" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA40" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="41" spans="1:27">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A41" s="43" t="s">
         <v>165</v>
       </c>
-      <c r="B41" s="56" t="s">
+      <c r="B41" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="57" t="s">
+      <c r="C41" s="55" t="s">
         <v>149</v>
       </c>
-      <c r="D41" s="57" t="s">
+      <c r="D41" s="55" t="s">
         <v>166</v>
       </c>
-      <c r="E41" s="57">
+      <c r="E41" s="55">
         <v>5247334240</v>
       </c>
-      <c r="F41" s="56" t="s">
+      <c r="F41" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G41" s="58" t="s">
+      <c r="G41" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="H41" s="56" t="s">
+      <c r="H41" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I41" s="56" t="s">
+      <c r="I41" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="56" t="s">
+      <c r="J41" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K41" s="57" t="s">
+      <c r="K41" s="55" t="s">
         <v>167</v>
       </c>
       <c r="L41" s="41" t="s">
@@ -6625,74 +6625,74 @@
         <v>37</v>
       </c>
       <c r="N41" s="42"/>
-      <c r="O41" s="56" t="s">
+      <c r="O41" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P41" s="56" t="s">
+      <c r="P41" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q41" s="59"/>
+      <c r="Q41" s="57"/>
       <c r="R41" s="45">
         <v>44926</v>
       </c>
-      <c r="S41" s="60">
+      <c r="S41" s="58">
         <v>45291</v>
       </c>
-      <c r="T41" s="57" t="s">
+      <c r="T41" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="U41" s="61" t="s">
+      <c r="U41" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V41" s="62" t="s">
+      <c r="V41" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="W41" s="56"/>
-      <c r="X41" s="56" t="s">
+      <c r="W41" s="54"/>
+      <c r="X41" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y41" s="56" t="s">
+      <c r="Y41" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z41" s="56" t="s">
+      <c r="Z41" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA41" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="42" spans="1:27">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A42" s="43" t="s">
         <v>168</v>
       </c>
-      <c r="B42" s="56" t="s">
+      <c r="B42" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="57" t="s">
+      <c r="C42" s="55" t="s">
         <v>149</v>
       </c>
-      <c r="D42" s="57" t="s">
+      <c r="D42" s="55" t="s">
         <v>169</v>
       </c>
-      <c r="E42" s="57">
+      <c r="E42" s="55">
         <v>5247334241</v>
       </c>
-      <c r="F42" s="56" t="s">
+      <c r="F42" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G42" s="58" t="s">
+      <c r="G42" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="H42" s="56" t="s">
+      <c r="H42" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I42" s="56" t="s">
+      <c r="I42" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J42" s="56" t="s">
+      <c r="J42" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K42" s="57" t="s">
+      <c r="K42" s="55" t="s">
         <v>170</v>
       </c>
       <c r="L42" s="41" t="s">
@@ -6702,74 +6702,74 @@
         <v>37</v>
       </c>
       <c r="N42" s="42"/>
-      <c r="O42" s="56" t="s">
+      <c r="O42" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P42" s="56" t="s">
+      <c r="P42" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q42" s="59"/>
+      <c r="Q42" s="57"/>
       <c r="R42" s="45">
         <v>44926</v>
       </c>
-      <c r="S42" s="60">
+      <c r="S42" s="58">
         <v>45291</v>
       </c>
-      <c r="T42" s="57" t="s">
+      <c r="T42" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="U42" s="61" t="s">
+      <c r="U42" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V42" s="62" t="s">
+      <c r="V42" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="W42" s="56"/>
-      <c r="X42" s="56" t="s">
+      <c r="W42" s="54"/>
+      <c r="X42" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y42" s="56" t="s">
+      <c r="Y42" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z42" s="56" t="s">
+      <c r="Z42" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA42" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="43" spans="1:27">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>171</v>
       </c>
-      <c r="B43" s="56" t="s">
+      <c r="B43" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="57" t="s">
+      <c r="C43" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="D43" s="57" t="s">
+      <c r="D43" s="55" t="s">
         <v>172</v>
       </c>
-      <c r="E43" s="57">
+      <c r="E43" s="55">
         <v>462417511</v>
       </c>
-      <c r="F43" s="56" t="s">
+      <c r="F43" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G43" s="58" t="s">
+      <c r="G43" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="H43" s="56" t="s">
+      <c r="H43" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I43" s="56" t="s">
+      <c r="I43" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J43" s="56" t="s">
+      <c r="J43" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K43" s="57" t="s">
+      <c r="K43" s="55" t="s">
         <v>173</v>
       </c>
       <c r="L43" s="41" t="s">
@@ -6779,221 +6779,221 @@
         <v>37</v>
       </c>
       <c r="N43" s="42"/>
-      <c r="O43" s="56" t="s">
+      <c r="O43" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P43" s="56" t="s">
+      <c r="P43" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q43" s="59"/>
+      <c r="Q43" s="57"/>
       <c r="R43" s="45">
         <v>44926</v>
       </c>
-      <c r="S43" s="60">
+      <c r="S43" s="58">
         <v>45291</v>
       </c>
-      <c r="T43" s="57" t="s">
+      <c r="T43" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U43" s="61" t="s">
+      <c r="U43" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V43" s="62" t="s">
+      <c r="V43" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="W43" s="56"/>
-      <c r="X43" s="56" t="s">
+      <c r="W43" s="54"/>
+      <c r="X43" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y43" s="56" t="s">
+      <c r="Y43" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z43" s="56" t="s">
+      <c r="Z43" s="54" t="s">
         <v>45</v>
       </c>
       <c r="AA43" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:27">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A44" s="43"/>
-      <c r="B44" s="56"/>
-      <c r="C44" s="71" t="s">
+      <c r="B44" s="54"/>
+      <c r="C44" s="69" t="s">
         <v>174</v>
       </c>
-      <c r="D44" s="71"/>
-      <c r="E44" s="71">
+      <c r="D44" s="69"/>
+      <c r="E44" s="69">
         <v>5229821458</v>
       </c>
-      <c r="F44" s="56" t="s">
+      <c r="F44" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G44" s="72" t="s">
+      <c r="G44" s="70" t="s">
         <v>175</v>
       </c>
-      <c r="H44" s="56" t="s">
+      <c r="H44" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I44" s="56" t="s">
+      <c r="I44" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J44" s="56" t="s">
+      <c r="J44" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K44" s="71"/>
+      <c r="K44" s="69"/>
       <c r="L44" s="41"/>
       <c r="M44" s="41"/>
       <c r="N44" s="42"/>
-      <c r="O44" s="56"/>
-      <c r="P44" s="56"/>
-      <c r="Q44" s="59"/>
+      <c r="O44" s="54"/>
+      <c r="P44" s="54"/>
+      <c r="Q44" s="57"/>
       <c r="R44" s="45"/>
-      <c r="S44" s="60"/>
-      <c r="T44" s="69" t="s">
+      <c r="S44" s="58"/>
+      <c r="T44" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="U44" s="61" t="s">
+      <c r="U44" s="59" t="s">
         <v>176</v>
       </c>
-      <c r="V44" s="62"/>
-      <c r="W44" s="56"/>
-      <c r="X44" s="56"/>
-      <c r="Y44" s="56"/>
-      <c r="Z44" s="56"/>
-    </row>
-    <row r="45" spans="1:27">
+      <c r="V44" s="60"/>
+      <c r="W44" s="54"/>
+      <c r="X44" s="54"/>
+      <c r="Y44" s="54"/>
+      <c r="Z44" s="54"/>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A45" s="43" t="s">
         <v>177</v>
       </c>
-      <c r="B45" s="56" t="s">
+      <c r="B45" s="54" t="s">
         <v>178</v>
       </c>
-      <c r="C45" s="57" t="s">
+      <c r="C45" s="55" t="s">
         <v>179</v>
       </c>
-      <c r="D45" s="73" t="s">
+      <c r="D45" s="71" t="s">
         <v>180</v>
       </c>
-      <c r="E45" s="57"/>
-      <c r="F45" s="56" t="s">
+      <c r="E45" s="55"/>
+      <c r="F45" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G45" s="58" t="s">
+      <c r="G45" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H45" s="56" t="s">
+      <c r="H45" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I45" s="56" t="s">
+      <c r="I45" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J45" s="56" t="s">
+      <c r="J45" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K45" s="64">
+      <c r="K45" s="62">
         <v>192168254240</v>
       </c>
       <c r="L45" s="41"/>
       <c r="M45" s="41"/>
       <c r="N45" s="42"/>
-      <c r="O45" s="56" t="s">
-        <v>38</v>
-      </c>
-      <c r="P45" s="56"/>
-      <c r="Q45" s="59"/>
+      <c r="O45" s="54" t="s">
+        <v>201</v>
+      </c>
+      <c r="P45" s="54"/>
+      <c r="Q45" s="57"/>
       <c r="R45" s="45">
         <v>44926</v>
       </c>
-      <c r="S45" s="60">
+      <c r="S45" s="58">
         <v>45291</v>
       </c>
-      <c r="T45" s="61"/>
-      <c r="U45" s="61" t="s">
+      <c r="T45" s="59"/>
+      <c r="U45" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V45" s="62"/>
-      <c r="W45" s="56"/>
-      <c r="X45" s="56" t="s">
+      <c r="V45" s="60"/>
+      <c r="W45" s="54"/>
+      <c r="X45" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="Y45" s="56" t="s">
+      <c r="Y45" s="54" t="s">
         <v>181</v>
       </c>
-      <c r="Z45" s="56"/>
-    </row>
-    <row r="46" spans="1:27">
+      <c r="Z45" s="54"/>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A46" s="43" t="s">
         <v>182</v>
       </c>
-      <c r="B46" s="56" t="s">
+      <c r="B46" s="54" t="s">
         <v>178</v>
       </c>
-      <c r="C46" s="57" t="s">
+      <c r="C46" s="55" t="s">
         <v>179</v>
       </c>
-      <c r="D46" s="73" t="s">
+      <c r="D46" s="71" t="s">
         <v>183</v>
       </c>
-      <c r="E46" s="61"/>
-      <c r="F46" s="56" t="s">
+      <c r="E46" s="59"/>
+      <c r="F46" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G46" s="58" t="s">
+      <c r="G46" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H46" s="56" t="s">
+      <c r="H46" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I46" s="56" t="s">
+      <c r="I46" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J46" s="56" t="s">
+      <c r="J46" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K46" s="64">
+      <c r="K46" s="62">
         <v>192168254241</v>
       </c>
       <c r="L46" s="41"/>
       <c r="M46" s="41"/>
       <c r="N46" s="42"/>
-      <c r="O46" s="56" t="s">
-        <v>38</v>
-      </c>
-      <c r="P46" s="56"/>
-      <c r="Q46" s="59"/>
+      <c r="O46" s="54" t="s">
+        <v>201</v>
+      </c>
+      <c r="P46" s="54"/>
+      <c r="Q46" s="57"/>
       <c r="R46" s="45">
         <v>44926</v>
       </c>
-      <c r="S46" s="60">
+      <c r="S46" s="58">
         <v>45291</v>
       </c>
-      <c r="T46" s="61"/>
-      <c r="U46" s="61" t="s">
+      <c r="T46" s="59"/>
+      <c r="U46" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V46" s="62"/>
-      <c r="W46" s="56"/>
-      <c r="X46" s="56" t="s">
+      <c r="V46" s="60"/>
+      <c r="W46" s="54"/>
+      <c r="X46" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="Y46" s="56" t="s">
+      <c r="Y46" s="54" t="s">
         <v>181</v>
       </c>
-      <c r="Z46" s="56"/>
+      <c r="Z46" s="54"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="D29:D42 D2:D16 D21:D27 D44:D46">
-    <cfRule type="duplicateValues" dxfId="61" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D43">
-    <cfRule type="duplicateValues" dxfId="60" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E43">
-    <cfRule type="duplicateValues" dxfId="59" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E44:E45 E2:E42">
-    <cfRule type="duplicateValues" dxfId="58" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="37"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -7104,37 +7104,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59F46541-D964-428E-8FFF-E7B5EABA90D0}">
   <dimension ref="A1:AA3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="16" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -7150,10 +7150,10 @@
       <c r="E1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="F1" s="72" t="s">
         <v>184</v>
       </c>
-      <c r="G1" s="55"/>
+      <c r="G1" s="73"/>
       <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
@@ -7215,7 +7215,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>124</v>
       </c>
@@ -7283,38 +7283,38 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:27">
-      <c r="A3" s="56" t="s">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A3" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="57" t="s">
+      <c r="C3" s="55" t="s">
         <v>187</v>
       </c>
-      <c r="D3" s="57" t="s">
+      <c r="D3" s="55" t="s">
         <v>188</v>
       </c>
-      <c r="E3" s="57">
+      <c r="E3" s="55">
         <v>535977548</v>
       </c>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="58" t="s">
+      <c r="G3" s="56" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="56" t="s">
+      <c r="H3" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="56" t="s">
+      <c r="I3" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="56" t="s">
+      <c r="J3" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="64">
+      <c r="K3" s="62">
         <v>192168254124</v>
       </c>
       <c r="L3" s="41" t="s">
@@ -7324,36 +7324,36 @@
         <v>37</v>
       </c>
       <c r="N3" s="42"/>
-      <c r="O3" s="56" t="s">
+      <c r="O3" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="P3" s="56" t="s">
+      <c r="P3" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="Q3" s="59"/>
+      <c r="Q3" s="57"/>
       <c r="R3" s="45">
         <v>44926</v>
       </c>
-      <c r="S3" s="60">
+      <c r="S3" s="58">
         <v>45291</v>
       </c>
-      <c r="T3" s="57" t="s">
+      <c r="T3" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="U3" s="61" t="s">
+      <c r="U3" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="V3" s="62" t="s">
+      <c r="V3" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="56"/>
-      <c r="X3" s="56" t="s">
+      <c r="W3" s="54"/>
+      <c r="X3" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="Y3" s="56" t="s">
+      <c r="Y3" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="Z3" s="56" t="s">
+      <c r="Z3" s="54" t="s">
         <v>45</v>
       </c>
     </row>
@@ -7361,14 +7361,14 @@
   <mergeCells count="1">
     <mergeCell ref="F1:G1"/>
   </mergeCells>
+  <conditionalFormatting sqref="D3">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E2">
-    <cfRule type="duplicateValues" dxfId="57" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D3">
-    <cfRule type="duplicateValues" dxfId="56" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3">
-    <cfRule type="duplicateValues" dxfId="55" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -7461,7 +7461,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61881701-EAD6-43B5-8E08-F81EF5284631}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7471,23 +7471,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC86DAB9-E93F-4170-BC3E-7568862C494D}">
   <dimension ref="B1:Z243"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5546875" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="12" max="12" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="16" max="16" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.7109375" customWidth="1"/>
-    <col min="22" max="22" width="9.42578125" customWidth="1"/>
-    <col min="26" max="26" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.6640625" customWidth="1"/>
+    <col min="22" max="22" width="9.44140625" customWidth="1"/>
+    <col min="26" max="26" width="15.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:26">
+    <row r="1" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
@@ -7528,7 +7528,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="2:26">
+    <row r="2" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>192</v>
       </c>
@@ -7570,7 +7570,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="2:26">
+    <row r="3" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>199</v>
       </c>
@@ -7612,7 +7612,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="4" spans="2:26">
+    <row r="4" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>178</v>
       </c>
@@ -7650,7 +7650,7 @@
       <c r="Y4" s="25"/>
       <c r="Z4" s="13"/>
     </row>
-    <row r="5" spans="2:26">
+    <row r="5" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>211</v>
       </c>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="Y5" s="25"/>
     </row>
-    <row r="6" spans="2:26">
+    <row r="6" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>219</v>
       </c>
@@ -7715,7 +7715,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="7" spans="2:26">
+    <row r="7" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>47</v>
       </c>
@@ -7735,7 +7735,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="8" spans="2:26">
+    <row r="8" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B8" s="5" t="s">
         <v>28</v>
       </c>
@@ -7750,7 +7750,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="9" spans="2:26">
+    <row r="9" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
       <c r="H9" s="7" t="s">
         <v>45</v>
@@ -7762,7 +7762,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="10" spans="2:26">
+    <row r="10" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B10" s="2"/>
       <c r="H10" s="7" t="s">
         <v>232</v>
@@ -7774,7 +7774,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="11" spans="2:26">
+    <row r="11" spans="2:26" x14ac:dyDescent="0.3">
       <c r="H11" s="7" t="s">
         <v>235</v>
       </c>
@@ -7783,7 +7783,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="12" spans="2:26">
+    <row r="12" spans="2:26" x14ac:dyDescent="0.3">
       <c r="H12" s="7" t="s">
         <v>237</v>
       </c>
@@ -7791,1158 +7791,1158 @@
         <v>238</v>
       </c>
     </row>
-    <row r="13" spans="2:26">
+    <row r="13" spans="2:26" x14ac:dyDescent="0.3">
       <c r="H13" s="7"/>
       <c r="T13" s="16" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="14" spans="2:26">
+    <row r="14" spans="2:26" x14ac:dyDescent="0.3">
       <c r="T14" s="16" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="15" spans="2:26">
+    <row r="15" spans="2:26" x14ac:dyDescent="0.3">
       <c r="T15" s="16" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="16" spans="2:26">
+    <row r="16" spans="2:26" x14ac:dyDescent="0.3">
       <c r="T16" s="16" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="17" spans="20:20">
+    <row r="17" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T17" s="16" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="18" spans="20:20">
+    <row r="18" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T18" s="16" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="19" spans="20:20">
+    <row r="19" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T19" s="16" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="20" spans="20:20">
+    <row r="20" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T20" s="16" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="21" spans="20:20">
+    <row r="21" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T21" s="16" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="22" spans="20:20">
+    <row r="22" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T22" s="16" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="23" spans="20:20">
+    <row r="23" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T23" s="16" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="24" spans="20:20">
+    <row r="24" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T24" s="16" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="25" spans="20:20">
+    <row r="25" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T25" s="16" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="26" spans="20:20">
+    <row r="26" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T26" s="16" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="27" spans="20:20">
+    <row r="27" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T27" s="16" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="28" spans="20:20">
+    <row r="28" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T28" s="16" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="29" spans="20:20">
+    <row r="29" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T29" s="16" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="30" spans="20:20">
+    <row r="30" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T30" s="16" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="31" spans="20:20">
+    <row r="31" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T31" s="16" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="32" spans="20:20">
+    <row r="32" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T32" s="16" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="33" spans="20:20">
+    <row r="33" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T33" s="16" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="34" spans="20:20">
+    <row r="34" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T34" s="16" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="35" spans="20:20">
+    <row r="35" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T35" s="16" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="36" spans="20:20">
+    <row r="36" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T36" s="16" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="37" spans="20:20">
+    <row r="37" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T37" s="16" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="38" spans="20:20">
+    <row r="38" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T38" s="16" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="39" spans="20:20">
+    <row r="39" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T39" s="16" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="40" spans="20:20">
+    <row r="40" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T40" s="16" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="41" spans="20:20">
+    <row r="41" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T41" s="16" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="42" spans="20:20">
+    <row r="42" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T42" s="16" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="43" spans="20:20">
+    <row r="43" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T43" s="16" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="44" spans="20:20">
+    <row r="44" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T44" s="16" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="45" spans="20:20">
+    <row r="45" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T45" s="16" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="46" spans="20:20">
+    <row r="46" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T46" s="16" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="47" spans="20:20">
+    <row r="47" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T47" s="16" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="48" spans="20:20">
+    <row r="48" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T48" s="16" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="49" spans="20:20">
+    <row r="49" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T49" s="16" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="50" spans="20:20">
+    <row r="50" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T50" s="16" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="51" spans="20:20">
+    <row r="51" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T51" s="16" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="52" spans="20:20">
+    <row r="52" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T52" s="16" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="53" spans="20:20">
+    <row r="53" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T53" s="16" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="54" spans="20:20">
+    <row r="54" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T54" s="16" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="55" spans="20:20">
+    <row r="55" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T55" s="16" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="56" spans="20:20">
+    <row r="56" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T56" s="16" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="57" spans="20:20">
+    <row r="57" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T57" s="16" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="58" spans="20:20">
+    <row r="58" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T58" s="16" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="59" spans="20:20">
+    <row r="59" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T59" s="16" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="60" spans="20:20">
+    <row r="60" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T60" s="16" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="61" spans="20:20">
+    <row r="61" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T61" s="16" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="62" spans="20:20">
+    <row r="62" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T62" s="16" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="63" spans="20:20">
+    <row r="63" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T63" s="16" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="64" spans="20:20">
+    <row r="64" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T64" s="16" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="65" spans="20:20">
+    <row r="65" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T65" s="16" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="66" spans="20:20">
+    <row r="66" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T66" s="16" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="67" spans="20:20">
+    <row r="67" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T67" s="16" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="68" spans="20:20">
+    <row r="68" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T68" s="16" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="69" spans="20:20">
+    <row r="69" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T69" s="16" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="70" spans="20:20">
+    <row r="70" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T70" s="16" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="71" spans="20:20">
+    <row r="71" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T71" s="16" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="72" spans="20:20">
+    <row r="72" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T72" s="16" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="73" spans="20:20">
+    <row r="73" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T73" s="16" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="74" spans="20:20">
+    <row r="74" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T74" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="75" spans="20:20">
+    <row r="75" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T75" s="16" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="76" spans="20:20">
+    <row r="76" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T76" s="16" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="77" spans="20:20">
+    <row r="77" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T77" s="16" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="78" spans="20:20">
+    <row r="78" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T78" s="16" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="79" spans="20:20">
+    <row r="79" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T79" s="16" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="80" spans="20:20">
+    <row r="80" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T80" s="16" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="81" spans="20:20">
+    <row r="81" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T81" s="16" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="82" spans="20:20">
+    <row r="82" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T82" s="16" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="83" spans="20:20">
+    <row r="83" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T83" s="16" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="84" spans="20:20">
+    <row r="84" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T84" s="16" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="85" spans="20:20">
+    <row r="85" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T85" s="16" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="86" spans="20:20">
+    <row r="86" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T86" s="16" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="87" spans="20:20">
+    <row r="87" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T87" s="16" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="88" spans="20:20">
+    <row r="88" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T88" s="16" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="89" spans="20:20">
+    <row r="89" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T89" s="16" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="90" spans="20:20">
+    <row r="90" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T90" s="16" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="91" spans="20:20">
+    <row r="91" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T91" s="16" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="92" spans="20:20">
+    <row r="92" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T92" s="16" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="93" spans="20:20">
+    <row r="93" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T93" s="16" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="94" spans="20:20">
+    <row r="94" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T94" s="16" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="95" spans="20:20">
+    <row r="95" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T95" s="16" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="96" spans="20:20">
+    <row r="96" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T96" s="16" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="97" spans="20:20">
+    <row r="97" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T97" s="16" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="98" spans="20:20">
+    <row r="98" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T98" s="16" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="99" spans="20:20">
+    <row r="99" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T99" s="16" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="100" spans="20:20">
+    <row r="100" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T100" s="16" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="101" spans="20:20">
+    <row r="101" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T101" s="16" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="102" spans="20:20">
+    <row r="102" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T102" s="16" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="103" spans="20:20">
+    <row r="103" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T103" s="16" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="104" spans="20:20">
+    <row r="104" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T104" s="16" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="105" spans="20:20">
+    <row r="105" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T105" s="16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="106" spans="20:20">
+    <row r="106" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T106" s="16" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="107" spans="20:20">
+    <row r="107" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T107" s="16" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="108" spans="20:20">
+    <row r="108" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T108" s="16" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="109" spans="20:20">
+    <row r="109" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T109" s="16" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="110" spans="20:20">
+    <row r="110" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T110" s="16" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="111" spans="20:20">
+    <row r="111" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T111" s="16" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="112" spans="20:20">
+    <row r="112" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T112" s="16" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="113" spans="20:20">
+    <row r="113" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T113" s="16" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="114" spans="20:20">
+    <row r="114" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T114" s="16" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="115" spans="20:20">
+    <row r="115" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T115" s="16" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="116" spans="20:20">
+    <row r="116" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T116" s="16" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="117" spans="20:20">
+    <row r="117" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T117" s="16" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="118" spans="20:20">
+    <row r="118" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T118" s="16" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="119" spans="20:20">
+    <row r="119" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T119" s="16" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="120" spans="20:20">
+    <row r="120" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T120" s="16" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="121" spans="20:20">
+    <row r="121" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T121" s="16" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="122" spans="20:20">
+    <row r="122" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T122" s="16" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="123" spans="20:20">
+    <row r="123" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T123" s="16" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="124" spans="20:20">
+    <row r="124" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T124" s="16" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="125" spans="20:20">
+    <row r="125" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T125" s="16" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="126" spans="20:20">
+    <row r="126" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T126" s="16" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="127" spans="20:20">
+    <row r="127" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T127" s="16" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="128" spans="20:20">
+    <row r="128" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T128" s="16" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="129" spans="20:20">
+    <row r="129" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T129" s="16" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="130" spans="20:20">
+    <row r="130" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T130" s="16" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="131" spans="20:20">
+    <row r="131" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T131" s="16" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="132" spans="20:20">
+    <row r="132" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T132" s="16" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="133" spans="20:20">
+    <row r="133" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T133" s="16" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="134" spans="20:20">
+    <row r="134" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T134" s="16" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="135" spans="20:20">
+    <row r="135" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T135" s="16" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="136" spans="20:20">
+    <row r="136" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T136" s="16" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="137" spans="20:20">
+    <row r="137" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T137" s="16" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="138" spans="20:20">
+    <row r="138" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T138" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="139" spans="20:20">
+    <row r="139" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T139" s="16" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="140" spans="20:20">
+    <row r="140" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T140" s="16" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="141" spans="20:20">
+    <row r="141" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T141" s="16" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="142" spans="20:20">
+    <row r="142" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T142" s="16" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="143" spans="20:20">
+    <row r="143" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T143" s="16" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="144" spans="20:20">
+    <row r="144" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T144" s="16" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="145" spans="20:20">
+    <row r="145" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T145" s="16" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="146" spans="20:20">
+    <row r="146" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T146" s="16" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="147" spans="20:20">
+    <row r="147" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T147" s="16" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="148" spans="20:20">
+    <row r="148" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T148" s="16" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="149" spans="20:20">
+    <row r="149" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T149" s="16" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="150" spans="20:20">
+    <row r="150" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T150" s="16" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="151" spans="20:20">
+    <row r="151" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T151" s="16" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="152" spans="20:20">
+    <row r="152" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T152" s="16" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="153" spans="20:20">
+    <row r="153" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T153" s="16" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="154" spans="20:20">
+    <row r="154" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T154" s="16" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="155" spans="20:20">
+    <row r="155" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T155" s="16" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="156" spans="20:20">
+    <row r="156" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T156" s="16" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="157" spans="20:20">
+    <row r="157" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T157" s="16" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="158" spans="20:20">
+    <row r="158" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T158" s="16" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="159" spans="20:20">
+    <row r="159" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T159" s="16" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="160" spans="20:20">
+    <row r="160" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T160" s="16" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="161" spans="20:20">
+    <row r="161" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T161" s="16" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="162" spans="20:20">
+    <row r="162" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T162" s="16" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="163" spans="20:20">
+    <row r="163" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T163" s="16" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="164" spans="20:20">
+    <row r="164" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T164" s="16" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="165" spans="20:20">
+    <row r="165" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T165" s="16" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="166" spans="20:20">
+    <row r="166" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T166" s="16" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="167" spans="20:20">
+    <row r="167" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T167" s="16" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="168" spans="20:20">
+    <row r="168" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T168" s="16" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="169" spans="20:20">
+    <row r="169" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T169" s="16" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="170" spans="20:20">
+    <row r="170" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T170" s="16" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="171" spans="20:20">
+    <row r="171" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T171" s="16" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="172" spans="20:20">
+    <row r="172" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T172" s="16" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="173" spans="20:20">
+    <row r="173" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T173" s="16" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="174" spans="20:20">
+    <row r="174" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T174" s="16" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="175" spans="20:20">
+    <row r="175" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T175" s="16" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="176" spans="20:20">
+    <row r="176" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T176" s="16" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="177" spans="20:20">
+    <row r="177" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T177" s="16" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="178" spans="20:20">
+    <row r="178" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T178" s="16" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="179" spans="20:20">
+    <row r="179" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T179" s="16" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="180" spans="20:20">
+    <row r="180" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T180" s="16" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="181" spans="20:20">
+    <row r="181" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T181" s="16" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="182" spans="20:20">
+    <row r="182" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T182" s="16" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="183" spans="20:20">
+    <row r="183" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T183" s="16" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="184" spans="20:20">
+    <row r="184" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T184" s="16" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="185" spans="20:20">
+    <row r="185" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T185" s="16" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="186" spans="20:20">
+    <row r="186" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T186" s="16" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="187" spans="20:20">
+    <row r="187" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T187" s="16" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="188" spans="20:20">
+    <row r="188" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T188" s="16" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="189" spans="20:20">
+    <row r="189" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T189" s="16" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="190" spans="20:20">
+    <row r="190" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T190" s="16" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="191" spans="20:20">
+    <row r="191" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T191" s="16" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="192" spans="20:20">
+    <row r="192" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T192" s="16" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="193" spans="20:20">
+    <row r="193" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T193" s="16" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="194" spans="20:20">
+    <row r="194" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T194" s="16" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="195" spans="20:20">
+    <row r="195" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T195" s="16" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="196" spans="20:20">
+    <row r="196" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T196" s="16" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="197" spans="20:20">
+    <row r="197" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T197" s="16" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="198" spans="20:20">
+    <row r="198" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T198" s="16" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="199" spans="20:20">
+    <row r="199" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T199" s="16" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="200" spans="20:20">
+    <row r="200" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T200" s="16" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="201" spans="20:20">
+    <row r="201" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T201" s="16" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="202" spans="20:20">
+    <row r="202" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T202" s="16" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="203" spans="20:20">
+    <row r="203" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T203" s="16" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="204" spans="20:20">
+    <row r="204" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T204" s="16" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="205" spans="20:20">
+    <row r="205" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T205" s="16" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="206" spans="20:20">
+    <row r="206" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T206" s="16" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="207" spans="20:20">
+    <row r="207" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T207" s="16" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="208" spans="20:20">
+    <row r="208" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T208" s="16" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="209" spans="20:20">
+    <row r="209" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T209" s="16" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="210" spans="20:20">
+    <row r="210" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T210" s="16" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="211" spans="20:20">
+    <row r="211" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T211" s="16" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="212" spans="20:20">
+    <row r="212" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T212" s="16" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="213" spans="20:20">
+    <row r="213" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T213" s="16" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="214" spans="20:20">
+    <row r="214" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T214" s="16" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="215" spans="20:20">
+    <row r="215" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T215" s="16" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="216" spans="20:20">
+    <row r="216" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T216" s="16" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="217" spans="20:20">
+    <row r="217" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T217" s="16" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="218" spans="20:20">
+    <row r="218" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T218" s="16" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="219" spans="20:20">
+    <row r="219" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T219" s="16" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="220" spans="20:20">
+    <row r="220" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T220" s="16" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="221" spans="20:20">
+    <row r="221" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T221" s="16" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="222" spans="20:20">
+    <row r="222" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T222" s="16" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="223" spans="20:20">
+    <row r="223" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T223" s="16" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="224" spans="20:20">
+    <row r="224" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T224" s="16" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="225" spans="20:20">
+    <row r="225" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T225" s="16" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="226" spans="20:20">
+    <row r="226" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T226" s="16" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="227" spans="20:20">
+    <row r="227" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T227" s="16" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="228" spans="20:20">
+    <row r="228" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T228" s="16" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="229" spans="20:20">
+    <row r="229" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T229" s="16" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="230" spans="20:20">
+    <row r="230" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T230" s="16" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="231" spans="20:20">
+    <row r="231" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T231" s="16" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="232" spans="20:20">
+    <row r="232" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T232" s="16" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="233" spans="20:20">
+    <row r="233" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T233" s="16" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="234" spans="20:20">
+    <row r="234" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T234" s="16" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="235" spans="20:20">
+    <row r="235" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T235" s="16" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="236" spans="20:20">
+    <row r="236" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T236" s="16" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="237" spans="20:20">
+    <row r="237" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T237" s="16" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="238" spans="20:20">
+    <row r="238" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T238" s="16" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="239" spans="20:20">
+    <row r="239" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T239" s="16" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="240" spans="20:20">
+    <row r="240" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T240" s="16" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="241" spans="20:20">
+    <row r="241" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T241" s="16" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="242" spans="20:20">
+    <row r="242" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T242" s="16" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="243" spans="20:20">
+    <row r="243" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T243" s="18" t="s">
         <v>467</v>
       </c>
@@ -8968,26 +8968,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="17703bd1-c751-4e43-b970-1dcca065b11e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="82a12f9a-4cc1-4c24-a90e-04ab0b7a8bc5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F0396F189DB75A4E9125D39B73600F53" ma:contentTypeVersion="19" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="4c0202d3d4844ea071972a0c64be0edd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="17703bd1-c751-4e43-b970-1dcca065b11e" xmlns:ns3="82a12f9a-4cc1-4c24-a90e-04ab0b7a8bc5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eee3c37956a584de5e2134a35da9d308" ns2:_="" ns3:_="">
     <xsd:import namespace="17703bd1-c751-4e43-b970-1dcca065b11e"/>
@@ -9236,14 +9216,60 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="17703bd1-c751-4e43-b970-1dcca065b11e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="82a12f9a-4cc1-4c24-a90e-04ab0b7a8bc5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E508A488-3332-440D-9FCB-C7067168C5CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A1569DB-5D8D-46B7-AB7B-C158A128691D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="17703bd1-c751-4e43-b970-1dcca065b11e"/>
+    <ds:schemaRef ds:uri="82a12f9a-4cc1-4c24-a90e-04ab0b7a8bc5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18253023-7171-4B6C-AF4A-36D31E1FC70E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18253023-7171-4B6C-AF4A-36D31E1FC70E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A1569DB-5D8D-46B7-AB7B-C158A128691D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E508A488-3332-440D-9FCB-C7067168C5CC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="17703bd1-c751-4e43-b970-1dcca065b11e"/>
+    <ds:schemaRef ds:uri="82a12f9a-4cc1-4c24-a90e-04ab0b7a8bc5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>